--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,6 +827,2292 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FK Suduva</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TransINVEST Vilnius</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SK Super Nova</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ogre United</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Hacken</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Djurgardens</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Keflavik</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Miramar Misiones</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Atenas</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Brusque FC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -875,7 +875,7 @@
         <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -1028,13 +1028,13 @@
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
@@ -1064,13 +1064,13 @@
         <v>28</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
         <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
         <v>4.4</v>
@@ -2904,10 +2904,10 @@
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2916,91 +2916,91 @@
         <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
         <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
         <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
         <v>1.95</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
         <v>30</v>
       </c>
       <c r="AA10" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK10" t="n">
         <v>30</v>
       </c>
-      <c r="AK10" t="n">
-        <v>27</v>
-      </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
         <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
         <v>5.4</v>
@@ -3009,43 +3009,43 @@
         <v>6.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC10" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC10" t="n">
-        <v>21</v>
-      </c>
       <c r="BD10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE10" t="n">
         <v>6.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>16.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG10" t="n">
         <v>6</v>
@@ -3054,13 +3054,13 @@
         <v>3.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3081,7 +3081,7 @@
         <v>8</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -881,7 +881,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.34</v>
@@ -890,130 +890,130 @@
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
         <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
         <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
         <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
         <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
         <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
         <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I4" t="n">
         <v>2.9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>1.08</v>
       </c>
       <c r="O6" t="n">
         <v>1.09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.66</v>
+        <v>1.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.73</v>
+        <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8</v>
+        <v>1.09</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6</v>
+        <v>2.54</v>
       </c>
       <c r="H7" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="I7" t="n">
         <v>3.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>7.8</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="H8" t="n">
         <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
         <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
@@ -2441,25 +2441,25 @@
         <v>27</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
@@ -2468,52 +2468,52 @@
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX8" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9</v>
       </c>
       <c r="AY8" t="n">
         <v>8.6</v>
@@ -2522,25 +2522,25 @@
         <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
         <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2552,16 +2552,16 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
         <v>3.45</v>
@@ -2570,13 +2570,13 @@
         <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR8" t="n">
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT8" t="n">
         <v>10</v>
@@ -2585,10 +2585,10 @@
         <v>5.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>55</v>
@@ -2597,14 +2597,14 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA8" t="n">
         <v>6.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.05</v>
+        <v>1.66</v>
       </c>
       <c r="Q9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -2904,10 +2904,10 @@
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2922,7 +2922,7 @@
         <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.27</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -860,7 +860,7 @@
         <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -872,7 +872,7 @@
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -881,7 +881,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
         <v>1.34</v>
@@ -890,13 +890,13 @@
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
         <v>1.77</v>
@@ -908,7 +908,7 @@
         <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
         <v>15</v>
@@ -917,106 +917,106 @@
         <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
         <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF2" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>18.5</v>
       </c>
-      <c r="AG2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.08</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>1.09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>2.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.08</v>
+        <v>1.73</v>
       </c>
       <c r="S6" t="n">
-        <v>1.09</v>
+        <v>1.8</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="H8" t="n">
         <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>4.9</v>
@@ -2411,7 +2411,7 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
         <v>1.69</v>
@@ -2429,10 +2429,10 @@
         <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
@@ -2441,7 +2441,7 @@
         <v>27</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
         <v>190</v>
@@ -2483,7 +2483,7 @@
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO8" t="n">
         <v>110</v>
@@ -2495,10 +2495,10 @@
         <v>17.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>8.199999999999999</v>
@@ -2510,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
         <v>8.800000000000001</v>
@@ -2522,7 +2522,7 @@
         <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
@@ -2531,16 +2531,16 @@
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -872,7 +872,7 @@
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -881,7 +881,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.34</v>
@@ -896,7 +896,7 @@
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.77</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G4" t="n">
         <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I4" t="n">
         <v>2.9</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="H6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="I6" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R6" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="G7" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I7" t="n">
         <v>3.65</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.3</v>
-      </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
         <v>190</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
         <v>12</v>
@@ -2486,7 +2486,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
         <v>16.5</v>
@@ -2495,10 +2495,10 @@
         <v>17.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT8" t="n">
         <v>8.199999999999999</v>
@@ -2510,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX8" t="n">
         <v>8.800000000000001</v>
@@ -2522,7 +2522,7 @@
         <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
@@ -2531,16 +2531,16 @@
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF8" t="n">
         <v>6.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
         <v>2.26</v>
@@ -2904,10 +2904,10 @@
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2919,7 +2919,7 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
         <v>2.18</v>
@@ -2931,7 +2931,7 @@
         <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
         <v>1.95</v>
@@ -2943,16 +2943,16 @@
         <v>1.8</v>
       </c>
       <c r="X10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
         <v>30</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB10" t="n">
         <v>9</v>
@@ -2997,16 +2997,16 @@
         <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -3015,40 +3015,40 @@
         <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD10" t="n">
         <v>6</v>
       </c>
-      <c r="AX10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="BE10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG10" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.1</v>
@@ -3066,10 +3066,10 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO10" t="n">
         <v>3.9</v>
@@ -3078,31 +3078,31 @@
         <v>17.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
         <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
         <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -881,7 +881,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
         <v>1.34</v>
@@ -896,7 +896,7 @@
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
         <v>1.77</v>
@@ -917,10 +917,10 @@
         <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
         <v>10.5</v>
@@ -932,7 +932,7 @@
         <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
         <v>16.5</v>
@@ -947,7 +947,7 @@
         <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="n">
         <v>29</v>
@@ -959,70 +959,70 @@
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO2" t="n">
         <v>42</v>
       </c>
       <c r="AP2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BA2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE2" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 11:30:34</t>
+          <t>2026-07-04 13:45:46</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
@@ -1141,200 +1141,200 @@
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.24</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 11:30:34</t>
+          <t>2026-07-04 13:45:46</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
         <v>2.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 11:30:34</t>
+          <t>2026-07-04 13:45:46</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G5" t="n">
         <v>3.65</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 11:30:34</t>
+          <t>2026-07-04 13:45:46</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>3.15</v>
       </c>
       <c r="G6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
         <v>1.94</v>
@@ -1891,133 +1891,133 @@
         <v>5.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.92</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AX6" t="n">
         <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
         <v>1.03</v>
@@ -2026,22 +2026,22 @@
         <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,7 +2053,7 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO6" t="n">
         <v>1.01</v>
@@ -2071,13 +2071,13 @@
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW6" t="n">
         <v>1.01</v>
@@ -2089,14 +2089,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA6" t="n">
         <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 11:30:34</t>
+          <t>2026-07-04 13:45:46</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
         <v>4.2</v>
@@ -2160,7 +2160,7 @@
         <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 11:30:34</t>
+          <t>2026-07-04 13:45:46</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H8" t="n">
         <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
@@ -2411,10 +2411,10 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
         <v>1.45</v>
@@ -2423,16 +2423,16 @@
         <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U8" t="n">
         <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
@@ -2441,13 +2441,13 @@
         <v>27</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
         <v>190</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
         <v>12</v>
@@ -2456,7 +2456,7 @@
         <v>28</v>
       </c>
       <c r="AE8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
@@ -2492,13 +2492,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>8.199999999999999</v>
@@ -2510,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
         <v>8.800000000000001</v>
@@ -2522,7 +2522,7 @@
         <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
@@ -2531,16 +2531,16 @@
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 11:30:34</t>
+          <t>2026-07-04 13:45:46</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 11:30:34</t>
+          <t>2026-07-04 13:45:46</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
         <v>3.2</v>
@@ -2907,73 +2907,73 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.27</v>
       </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AB10" t="n">
         <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>80</v>
@@ -2985,76 +2985,76 @@
         <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA10" t="n">
         <v>4.7</v>
       </c>
-      <c r="AY10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BB10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH10" t="n">
         <v>3.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3069,16 +3069,16 @@
         <v>13</v>
       </c>
       <c r="BN10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR10" t="n">
         <v>36</v>
@@ -3087,10 +3087,10 @@
         <v>10</v>
       </c>
       <c r="BT10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3099,7 +3099,7 @@
         <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
         <v>11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 11:30:34</t>
+          <t>2026-07-04 13:45:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,7 +875,7 @@
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -896,7 +896,7 @@
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
         <v>1.77</v>
@@ -929,7 +929,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -965,76 +965,76 @@
         <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA2" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2" t="n">
         <v>6.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
@@ -1046,16 +1046,16 @@
         <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU2" t="n">
         <v>5</v>
@@ -1064,13 +1064,13 @@
         <v>28</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
         <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 13:45:46</t>
+          <t>2026-07-04 16:01:15</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1141,7 +1141,7 @@
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q3" t="n">
         <v>1.24</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 13:45:46</t>
+          <t>2026-07-04 16:01:15</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
         <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
         <v>2.9</v>
@@ -1383,212 +1383,212 @@
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
         <v>2.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 13:45:46</t>
+          <t>2026-07-04 16:01:15</t>
         </is>
       </c>
     </row>
@@ -1622,234 +1622,234 @@
         <v>3.4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
         <v>2.26</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 13:45:46</t>
+          <t>2026-07-04 16:01:15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.15</v>
+        <v>2.26</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>2.58</v>
       </c>
       <c r="H6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.94</v>
       </c>
-      <c r="I6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.38</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ6" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 13:45:46</t>
+          <t>2026-07-04 16:01:15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.26</v>
+        <v>1.56</v>
       </c>
       <c r="G7" t="n">
-        <v>2.58</v>
+        <v>1.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="I7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO7" t="n">
         <v>3.45</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 13:45:46</t>
+          <t>2026-07-04 16:01:15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 13:45:46</t>
+          <t>2026-07-04 16:01:15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,229 +2626,229 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,261 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 13:45:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Brusque FC</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Figueirense</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="X10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-07-04 13:45:46</t>
+          <t>2026-07-04 16:01:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,7 +875,7 @@
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         <v>1.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S3" t="n">
         <v>1.24</v>
@@ -1159,7 +1159,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.18</v>
@@ -1404,7 +1404,7 @@
         <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
@@ -1419,112 +1419,112 @@
         <v>1.61</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
         <v>6</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BN4" t="n">
         <v>8.6</v>
@@ -1554,13 +1554,13 @@
         <v>25</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
@@ -1572,23 +1572,23 @@
         <v>28</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BX4" t="n">
         <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BZ4" t="n">
         <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1646,7 +1646,7 @@
         <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
@@ -1667,10 +1667,10 @@
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
         <v>19</v>
@@ -1763,16 +1763,16 @@
         <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD5" t="n">
         <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
         <v>4.8</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN5" t="n">
         <v>6.8</v>
@@ -1808,13 +1808,13 @@
         <v>28</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR5" t="n">
         <v>38</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT5" t="n">
         <v>5.2</v>
@@ -1826,30 +1826,30 @@
         <v>16.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>29</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>25</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="I6" t="n">
-        <v>3.45</v>
+        <v>2.18</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.56</v>
+        <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>2.58</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="I7" t="n">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>1.82</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="S7" t="n">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>2.42</v>
+        <v>1.64</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,498 +2367,752 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-04 18:15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Brusque FC</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Figueirense</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>2.18</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="n">
         <v>4.1</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>4.8</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>3.2</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>3.55</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="L10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M10" t="n">
         <v>1.09</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N10" t="n">
         <v>3.05</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="O10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>2.2</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1.26</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>4.2</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>1.92</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>1.91</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V10" t="n">
         <v>1.27</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W10" t="n">
         <v>1.85</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X10" t="n">
         <v>13</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y10" t="n">
         <v>16</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z10" t="n">
         <v>38</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA10" t="n">
         <v>120</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB10" t="n">
         <v>9</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD10" t="n">
         <v>22</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE10" t="n">
         <v>75</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AF10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AH10" t="n">
         <v>24</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AI10" t="n">
         <v>90</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AJ10" t="n">
         <v>34</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK10" t="n">
         <v>30</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AL10" t="n">
         <v>55</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AM10" t="n">
         <v>160</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AN10" t="n">
         <v>24</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AO10" t="n">
         <v>95</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AP10" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AR10" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AS10" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
+      <c r="AT10" t="n">
         <v>6</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV10" t="n">
         <v>14</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AW10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AX10" t="n">
         <v>9.4</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AY10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="AZ10" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BA10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BB10" t="n">
         <v>20</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BC10" t="n">
         <v>19</v>
       </c>
-      <c r="BD9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE9" t="n">
+      <c r="BD10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE10" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BF10" t="n">
         <v>15.5</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BG10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BH10" t="n">
         <v>3.1</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BI10" t="n">
         <v>2.54</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BK10" t="n">
         <v>6</v>
       </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>13</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BN10" t="n">
         <v>4.8</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BO10" t="n">
         <v>3.8</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BP10" t="n">
         <v>16.5</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BQ10" t="n">
         <v>7.6</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="BR10" t="n">
         <v>36</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="BS10" t="n">
         <v>10</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="BT10" t="n">
         <v>7.4</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="BU10" t="n">
         <v>5.7</v>
       </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
         <v>10</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="BX10" t="n">
         <v>55</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="BY10" t="n">
         <v>11</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-07-04 16:01:15</t>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 18:15:42</t>
+          <t>2026-07-04 20:29:13</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 18:15:42</t>
+          <t>2026-07-04 20:29:13</t>
         </is>
       </c>
     </row>
@@ -1395,16 +1395,16 @@
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
@@ -1527,68 +1527,68 @@
         <v>11.5</v>
       </c>
       <c r="BH4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN4" t="n">
         <v>6</v>
       </c>
-      <c r="BI4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK4" t="n">
+      <c r="BO4" t="n">
         <v>5.3</v>
       </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BP4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.62</v>
+        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4" t="n">
         <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.72</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 18:15:42</t>
+          <t>2026-07-04 20:29:13</t>
         </is>
       </c>
     </row>
@@ -1628,13 +1628,13 @@
         <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1652,7 +1652,7 @@
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
@@ -1667,7 +1667,7 @@
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W5" t="n">
         <v>1.38</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 18:15:42</t>
+          <t>2026-07-04 20:29:13</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 18:15:42</t>
+          <t>2026-07-04 20:29:13</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
         <v>2.58</v>
@@ -2142,19 +2142,19 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.82</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
         <v>1.82</v>
@@ -2163,16 +2163,16 @@
         <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
         <v>1.4</v>
@@ -2181,166 +2181,166 @@
         <v>1.64</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 18:15:42</t>
+          <t>2026-07-04 20:29:13</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>5.6</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
@@ -2417,7 +2417,7 @@
         <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
         <v>2.5</v>
@@ -2429,7 +2429,7 @@
         <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
         <v>2.48</v>
@@ -2471,7 +2471,7 @@
         <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK8" t="n">
         <v>18</v>
@@ -2486,28 +2486,28 @@
         <v>7.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS8" t="n">
         <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW8" t="n">
         <v>4.9</v>
@@ -2516,7 +2516,7 @@
         <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
         <v>16.5</v>
@@ -2528,7 +2528,7 @@
         <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD8" t="n">
         <v>4.5</v>
@@ -2537,10 +2537,10 @@
         <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="n">
         <v>4.4</v>
@@ -2564,13 +2564,13 @@
         <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP8" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
         <v>22</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 18:15:42</t>
+          <t>2026-07-04 20:29:13</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
         <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 18:15:42</t>
+          <t>2026-07-04 20:29:13</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
         <v>4.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 18:15:42</t>
+          <t>2026-07-04 20:29:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -875,7 +875,7 @@
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -1141,13 +1141,13 @@
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
         <v>1.24</v>
@@ -1159,7 +1159,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -1383,10 +1383,10 @@
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
         <v>5.6</v>
@@ -1395,7 +1395,7 @@
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
@@ -1422,7 +1422,7 @@
         <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z4" t="n">
         <v>28</v>
@@ -1431,13 +1431,13 @@
         <v>50</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AC4" t="n">
         <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>32</v>
@@ -1449,7 +1449,7 @@
         <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AI4" t="n">
         <v>38</v>
@@ -1467,58 +1467,58 @@
         <v>65</v>
       </c>
       <c r="AN4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO4" t="n">
         <v>16.5</v>
       </c>
-      <c r="AO4" t="n">
-        <v>19</v>
-      </c>
       <c r="AP4" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU4" t="n">
         <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
         <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R6" t="n">
         <v>1.87</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G7" t="n">
         <v>2.58</v>
@@ -2277,7 +2277,7 @@
         <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BE7" t="n">
         <v>7.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G8" t="n">
         <v>1.67</v>
@@ -2396,7 +2396,7 @@
         <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.26</v>
@@ -2414,7 +2414,7 @@
         <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
         <v>1.54</v>
@@ -2438,10 +2438,10 @@
         <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
         <v>170</v>
@@ -2471,7 +2471,7 @@
         <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK8" t="n">
         <v>18</v>
@@ -2495,10 +2495,10 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT8" t="n">
         <v>9.4</v>
@@ -2510,7 +2510,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
         <v>8.6</v>
@@ -2522,7 +2522,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2531,22 +2531,22 @@
         <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
         <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="n">
         <v>4.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
@@ -2564,47 +2564,47 @@
         <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP8" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS8" t="n">
         <v>6.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
         <v>48</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="G9" t="n">
         <v>2.02</v>
@@ -2644,7 +2644,7 @@
         <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
@@ -2668,7 +2668,7 @@
         <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
         <v>1.23</v>
@@ -2695,19 +2695,19 @@
         <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
         <v>180</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
         <v>110</v>
@@ -2737,7 +2737,7 @@
         <v>210</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
         <v>160</v>
@@ -2749,10 +2749,10 @@
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2764,19 +2764,19 @@
         <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
         <v>19</v>
@@ -2785,16 +2785,16 @@
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF9" t="n">
         <v>14</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="n">
         <v>3.05</v>
@@ -2818,7 +2818,7 @@
         <v>4.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
         <v>15.5</v>
@@ -2836,7 +2836,7 @@
         <v>8.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G10" t="n">
         <v>2.18</v>
@@ -2907,7 +2907,7 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2916,7 +2916,7 @@
         <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
         <v>1.7</v>
@@ -2928,7 +2928,7 @@
         <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
         <v>1.92</v>
@@ -3009,7 +3009,7 @@
         <v>4.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,7 +875,7 @@
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1162,7 +1162,7 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1222,10 +1222,10 @@
         <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
         <v>1.03</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I4" t="n">
         <v>2.9</v>
@@ -1476,10 +1476,10 @@
         <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS4" t="n">
         <v>5.3</v>
@@ -1491,7 +1491,7 @@
         <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
         <v>5.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G5" t="n">
         <v>3.6</v>
@@ -1646,7 +1646,7 @@
         <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
         <v>18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="AR8" t="n">
         <v>4.9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="G9" t="n">
         <v>2.02</v>
@@ -2653,7 +2653,7 @@
         <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2916,7 +2916,7 @@
         <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
         <v>1.7</v>
@@ -3112,7 +3112,515 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:54:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>8</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -860,13 +860,13 @@
         <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -875,7 +875,7 @@
         <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -905,10 +905,10 @@
         <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
         <v>15</v>
@@ -971,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>5.7</v>
       </c>
       <c r="AS2" t="n">
         <v>6.6</v>
@@ -983,40 +983,40 @@
         <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>5.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
         <v>6.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>19</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G3" t="n">
         <v>1.86</v>
@@ -1159,7 +1159,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
         <v>2.16</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G4" t="n">
         <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1389,13 +1389,13 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O4" t="n">
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
@@ -1404,7 +1404,7 @@
         <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
@@ -1422,13 +1422,13 @@
         <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="n">
         <v>17.5</v>
@@ -1437,94 +1437,94 @@
         <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>15</v>
       </c>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN4" t="n">
         <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AU4" t="n">
         <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH4" t="n">
         <v>4.5</v>
@@ -1536,13 +1536,13 @@
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN4" t="n">
         <v>6</v>
@@ -1554,7 +1554,7 @@
         <v>17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
@@ -1569,7 +1569,7 @@
         <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BW4" t="n">
         <v>8.199999999999999</v>
@@ -1578,17 +1578,17 @@
         <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="CA4" t="n">
         <v>7.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
         <v>2.32</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1643,7 +1643,7 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
@@ -1655,10 +1655,10 @@
         <v>1.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
         <v>1.73</v>
@@ -1736,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT5" t="n">
         <v>12.5</v>
@@ -1760,22 +1760,22 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG5" t="n">
         <v>14.5</v>
@@ -1784,7 +1784,7 @@
         <v>3.45</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
         <v>2.58</v>
@@ -2145,7 +2145,7 @@
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -2184,10 +2184,10 @@
         <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
@@ -2199,10 +2199,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
         <v>16</v>
@@ -2217,7 +2217,7 @@
         <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
@@ -2229,13 +2229,13 @@
         <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>9.800000000000001</v>
@@ -2256,10 +2256,10 @@
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
@@ -2274,13 +2274,13 @@
         <v>27</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BD7" t="n">
         <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
         <v>17.5</v>
@@ -2289,58 +2289,58 @@
         <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.31</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.31</v>
+        <v>8.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.31</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.31</v>
+        <v>7.2</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.31</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.31</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.31</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -2405,16 +2405,16 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
         <v>1.54</v>
@@ -2426,7 +2426,7 @@
         <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
@@ -2474,7 +2474,7 @@
         <v>16.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
         <v>34</v>
@@ -2483,7 +2483,7 @@
         <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO8" t="n">
         <v>80</v>
@@ -2492,13 +2492,13 @@
         <v>18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT8" t="n">
         <v>9.4</v>
@@ -2510,7 +2510,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX8" t="n">
         <v>8.6</v>
@@ -2522,7 +2522,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2531,16 +2531,16 @@
         <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF8" t="n">
         <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH8" t="n">
         <v>4.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="G9" t="n">
         <v>2.02</v>
@@ -2644,16 +2644,16 @@
         <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
         <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2683,10 +2683,10 @@
         <v>1.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X9" t="n">
         <v>11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -2901,13 +2901,13 @@
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2919,10 +2919,10 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.26</v>
@@ -2931,10 +2931,10 @@
         <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V10" t="n">
         <v>1.27</v>
@@ -2961,13 +2961,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -2979,10 +2979,10 @@
         <v>90</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
         <v>55</v>
@@ -2994,7 +2994,7 @@
         <v>24</v>
       </c>
       <c r="AO10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
         <v>8.6</v>
@@ -3003,13 +3003,13 @@
         <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU10" t="n">
         <v>6</v>
@@ -3018,7 +3018,7 @@
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
         <v>9.4</v>
@@ -3030,7 +3030,7 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -3039,70 +3039,70 @@
         <v>19</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
         <v>15.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI10" t="n">
         <v>2.54</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO10" t="n">
         <v>3.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
         <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU10" t="n">
         <v>5.7</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW10" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -3164,25 +3164,25 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="P11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="R11" t="n">
         <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>
@@ -3397,25 +3397,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -3427,10 +3427,10 @@
         <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R12" t="n">
         <v>1.28</v>
@@ -3439,22 +3439,22 @@
         <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
         <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X12" t="n">
         <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
         <v>40</v>
@@ -3463,7 +3463,7 @@
         <v>150</v>
       </c>
       <c r="AB12" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
         <v>8.6</v>
@@ -3475,31 +3475,31 @@
         <v>90</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
         <v>95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>110</v>
@@ -3514,7 +3514,7 @@
         <v>28</v>
       </c>
       <c r="AS12" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
         <v>6.8</v>
@@ -3526,7 +3526,7 @@
         <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>9.4</v>
@@ -3538,31 +3538,31 @@
         <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
         <v>18</v>
       </c>
       <c r="BC12" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
         <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
         <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12" t="n">
         <v>3.3</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3583,25 +3583,25 @@
         <v>3.85</v>
       </c>
       <c r="BP12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR12" t="n">
         <v>32</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU12" t="n">
         <v>6.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW12" t="n">
         <v>8.800000000000001</v>
@@ -3616,11 +3616,11 @@
         <v>29</v>
       </c>
       <c r="CA12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -872,10 +872,10 @@
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -971,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
         <v>6.6</v>
@@ -983,31 +983,31 @@
         <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>25</v>
+        <v>6.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
         <v>6.8</v>
@@ -1016,7 +1016,7 @@
         <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>25</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
         <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1392,7 +1392,7 @@
         <v>5.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
         <v>2.58</v>
@@ -1410,7 +1410,7 @@
         <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V4" t="n">
         <v>1.53</v>
@@ -1461,28 +1461,28 @@
         <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
         <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
         <v>14.5</v>
@@ -1494,10 +1494,10 @@
         <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1506,19 +1506,19 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB4" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD4" t="n">
         <v>7.2</v>
       </c>
-      <c r="BD4" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
@@ -1530,7 +1530,7 @@
         <v>4.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -1637,13 +1637,13 @@
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
@@ -1670,7 +1670,7 @@
         <v>1.75</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
         <v>19</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="n">
         <v>3.75</v>
@@ -1882,7 +1882,7 @@
         <v>1.94</v>
       </c>
       <c r="I6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J6" t="n">
         <v>3.9</v>
@@ -1912,22 +1912,22 @@
         <v>1.87</v>
       </c>
       <c r="S6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U6" t="n">
         <v>2.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W6" t="n">
         <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y6" t="n">
         <v>23</v>
@@ -1942,13 +1942,13 @@
         <v>30</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
         <v>38</v>
@@ -1984,7 +1984,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR6" t="n">
         <v>15</v>
@@ -2035,28 +2035,28 @@
         <v>5.7</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>13.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2092,11 +2092,11 @@
         <v>11.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -2217,13 +2217,13 @@
         <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
         <v>120</v>
@@ -2244,7 +2244,7 @@
         <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>44</v>
+        <v>7.8</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
@@ -2256,7 +2256,7 @@
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX7" t="n">
         <v>5.7</v>
@@ -2265,7 +2265,7 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
         <v>38</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
         <v>1.54</v>
@@ -2474,7 +2474,7 @@
         <v>16.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL8" t="n">
         <v>34</v>
@@ -2495,10 +2495,10 @@
         <v>4.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>9.4</v>
@@ -2510,7 +2510,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
         <v>8.6</v>
@@ -2522,7 +2522,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2531,16 +2531,16 @@
         <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF8" t="n">
         <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH8" t="n">
         <v>4.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2674,7 +2674,7 @@
         <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
         <v>2.06</v>
@@ -2698,7 +2698,7 @@
         <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB9" t="n">
         <v>7.4</v>
@@ -2707,7 +2707,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>110</v>
@@ -2725,7 +2725,7 @@
         <v>120</v>
       </c>
       <c r="AJ9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
@@ -2749,10 +2749,10 @@
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2764,19 +2764,19 @@
         <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
         <v>19</v>
@@ -2785,16 +2785,16 @@
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
         <v>14</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="n">
         <v>3.05</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2922,7 +2922,7 @@
         <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
         <v>1.26</v>
@@ -2949,7 +2949,7 @@
         <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA10" t="n">
         <v>120</v>
@@ -2964,7 +2964,7 @@
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
         <v>14</v>
@@ -2976,19 +2976,19 @@
         <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
         <v>24</v>
@@ -2997,58 +2997,58 @@
         <v>85</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.6</v>
+        <v>3.95</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
         <v>6.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>4.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>15.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH10" t="n">
         <v>3.15</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -3143,154 +3143,154 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>1.07</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.08</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>1.08</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
         <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
         <v>1.03</v>
@@ -3305,13 +3305,13 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK11" t="n">
         <v>1.01</v>
@@ -3323,31 +3323,31 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO11" t="n">
         <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS11" t="n">
         <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU11" t="n">
         <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW11" t="n">
         <v>1.01</v>
@@ -3359,14 +3359,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA11" t="n">
         <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -3427,13 +3427,13 @@
         <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
         <v>2.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
         <v>3.75</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -866,16 +866,16 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -887,7 +887,7 @@
         <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
@@ -905,7 +905,7 @@
         <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
         <v>1.6</v>
@@ -914,10 +914,10 @@
         <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
         <v>65</v>
@@ -932,7 +932,7 @@
         <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
         <v>16.5</v>
@@ -953,19 +953,19 @@
         <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
         <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -986,7 +986,7 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
         <v>13</v>
@@ -998,31 +998,31 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC2" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G3" t="n">
         <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,16 +1135,16 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R3" t="n">
         <v>1.07</v>
@@ -1153,13 +1153,13 @@
         <v>1.24</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U3" t="n">
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
         <v>2.16</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
         <v>2.62</v>
@@ -1374,7 +1374,7 @@
         <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1392,10 +1392,10 @@
         <v>5.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
@@ -1410,7 +1410,7 @@
         <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V4" t="n">
         <v>1.53</v>
@@ -1428,22 +1428,22 @@
         <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
         <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
@@ -1452,37 +1452,37 @@
         <v>15</v>
       </c>
       <c r="AI4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN4" t="n">
         <v>13.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
       </c>
       <c r="AR4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS4" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
         <v>14.5</v>
@@ -1494,7 +1494,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="AX4" t="n">
         <v>17.5</v>
@@ -1506,19 +1506,19 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE4" t="n">
         <v>7</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
@@ -1530,13 +1530,13 @@
         <v>4.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1554,10 +1554,10 @@
         <v>17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BS4" t="n">
         <v>9.199999999999999</v>
@@ -1569,13 +1569,13 @@
         <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BX4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>9.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1622,22 @@
         <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1652,79 +1652,79 @@
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W5" t="n">
         <v>1.39</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
         <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
         <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
         <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AP5" t="n">
         <v>13.5</v>
@@ -1733,64 +1733,64 @@
         <v>9.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.3</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
         <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>44</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.4</v>
+        <v>32</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>38</v>
       </c>
       <c r="BE5" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK5" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>7.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,25 +1802,25 @@
         <v>6.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BP5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BQ5" t="n">
         <v>10</v>
       </c>
       <c r="BR5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT5" t="n">
         <v>5.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
         <v>16.5</v>
@@ -1835,14 +1835,14 @@
         <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
         <v>1.94</v>
       </c>
       <c r="I6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J6" t="n">
         <v>3.9</v>
@@ -1894,7 +1894,7 @@
         <v>1.19</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
         <v>7.2</v>
@@ -1906,22 +1906,22 @@
         <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
         <v>1.93</v>
       </c>
       <c r="T6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U6" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="W6" t="n">
         <v>1.37</v>
@@ -1930,7 +1930,7 @@
         <v>44</v>
       </c>
       <c r="Y6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z6" t="n">
         <v>23</v>
@@ -1942,16 +1942,16 @@
         <v>30</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
         <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AG6" t="n">
         <v>19</v>
@@ -1960,13 +1960,13 @@
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AJ6" t="n">
         <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
         <v>36</v>
@@ -1978,13 +1978,13 @@
         <v>18.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AP6" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
         <v>15</v>
@@ -1996,16 +1996,16 @@
         <v>19.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AY6" t="n">
         <v>12.5</v>
@@ -2014,13 +2014,13 @@
         <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
         <v>1.03</v>
@@ -2032,13 +2032,13 @@
         <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="n">
         <v>5.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -2127,139 +2127,139 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
         <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X7" t="n">
         <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS7" t="n">
         <v>42</v>
       </c>
-      <c r="AK7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AT7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
@@ -2268,34 +2268,34 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
         <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG7" t="n">
         <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
         <v>4.8</v>
@@ -2304,31 +2304,31 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP7" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
         <v>7.2</v>
       </c>
       <c r="BT7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,7 +2340,7 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.54</v>
       </c>
       <c r="G8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="H8" t="n">
         <v>5.6</v>
@@ -2393,7 +2393,7 @@
         <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
         <v>5.1</v>
@@ -2420,10 +2420,10 @@
         <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
         <v>2.16</v>
@@ -2432,22 +2432,22 @@
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="X8" t="n">
         <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
         <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
         <v>12.5</v>
@@ -2459,10 +2459,10 @@
         <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>23</v>
@@ -2471,7 +2471,7 @@
         <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AK8" t="n">
         <v>18</v>
@@ -2483,16 +2483,16 @@
         <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="AR8" t="n">
         <v>5</v>
@@ -2504,7 +2504,7 @@
         <v>9.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV8" t="n">
         <v>19.5</v>
@@ -2513,10 +2513,10 @@
         <v>5.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
         <v>16.5</v>
@@ -2525,10 +2525,10 @@
         <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC8" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
         <v>4.7</v>
@@ -2537,7 +2537,7 @@
         <v>5.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG8" t="n">
         <v>5.1</v>
@@ -2549,19 +2549,19 @@
         <v>3.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO8" t="n">
         <v>3.55</v>
@@ -2570,41 +2570,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BR8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT8" t="n">
         <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV8" t="n">
         <v>48</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.91</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>4.7</v>
@@ -2647,19 +2647,19 @@
         <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.46</v>
@@ -2671,28 +2671,28 @@
         <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V9" t="n">
         <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
         <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
         <v>40</v>
@@ -2704,7 +2704,7 @@
         <v>7.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
         <v>22</v>
@@ -2728,10 +2728,10 @@
         <v>24</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
         <v>210</v>
@@ -2749,10 +2749,10 @@
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2764,19 +2764,19 @@
         <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
         <v>19</v>
@@ -2785,16 +2785,16 @@
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="n">
         <v>3.05</v>
@@ -2806,13 +2806,13 @@
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
         <v>4.5</v>
@@ -2830,7 +2830,7 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
         <v>8.6</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H10" t="n">
         <v>4.1</v>
@@ -2907,7 +2907,7 @@
         <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2931,7 +2931,7 @@
         <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U10" t="n">
         <v>1.9</v>
@@ -2940,7 +2940,7 @@
         <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2949,7 +2949,7 @@
         <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
         <v>120</v>
@@ -2964,7 +2964,7 @@
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
         <v>14</v>
@@ -2976,79 +2976,79 @@
         <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN10" t="n">
         <v>24</v>
       </c>
       <c r="AO10" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.95</v>
+        <v>8.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS10" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AT10" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>36</v>
-      </c>
       <c r="BE10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.6</v>
+        <v>15.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="n">
         <v>3.15</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="H11" t="n">
         <v>5.1</v>
@@ -3194,7 +3194,7 @@
         <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -3212,7 +3212,7 @@
         <v>7.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
         <v>34</v>
@@ -3251,58 +3251,58 @@
         <v>320</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="n">
         <v>2.92</v>
@@ -3314,59 +3314,59 @@
         <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BN11" t="n">
         <v>4.3</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BP11" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>42</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT11" t="n">
         <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BZ11" t="n">
         <v>38</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>
@@ -3400,22 +3400,22 @@
         <v>1.79</v>
       </c>
       <c r="G12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
         <v>5.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -3433,7 +3433,7 @@
         <v>2.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
         <v>3.75</v>
@@ -3445,13 +3445,13 @@
         <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>2.04</v>
       </c>
       <c r="X12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
         <v>16.5</v>
@@ -3472,7 +3472,7 @@
         <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
         <v>11.5</v>
@@ -3484,52 +3484,52 @@
         <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="n">
         <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP12" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12" t="n">
         <v>8.800000000000001</v>
@@ -3538,25 +3538,25 @@
         <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>18</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
         <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="n">
         <v>3.3</v>
@@ -3607,7 +3607,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
         <v>9.199999999999999</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,16 +866,16 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -887,7 +887,7 @@
         <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
@@ -905,7 +905,7 @@
         <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.6</v>
@@ -920,7 +920,7 @@
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
         <v>10.5</v>
@@ -986,7 +986,7 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>13</v>
@@ -1010,13 +1010,13 @@
         <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
         <v>19.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
         <v>1.86</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
         <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I4" t="n">
         <v>2.9</v>
@@ -1380,10 +1380,10 @@
         <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1536,7 +1536,7 @@
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1554,7 +1554,7 @@
         <v>17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BR4" t="n">
         <v>24</v>
@@ -1572,7 +1572,7 @@
         <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
@@ -1628,16 +1628,16 @@
         <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1646,13 +1646,13 @@
         <v>3.95</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
@@ -1661,10 +1661,10 @@
         <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V5" t="n">
         <v>1.74</v>
@@ -1688,7 +1688,7 @@
         <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
         <v>11.5</v>
@@ -1715,7 +1715,7 @@
         <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1730,13 +1730,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
         <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1757,13 +1757,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BC5" t="n">
         <v>32</v>
@@ -1772,7 +1772,7 @@
         <v>38</v>
       </c>
       <c r="BE5" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BF5" t="n">
         <v>23</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>CSD Yupanqui</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>7.2</v>
+        <v>1.08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>1.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="T6" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
         <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,234 +2113,234 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Club Mercedes</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>1.08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>1.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.54</v>
+        <v>3.25</v>
       </c>
       <c r="G8" t="n">
-        <v>1.59</v>
+        <v>3.7</v>
       </c>
       <c r="H8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X8" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH8" t="n">
         <v>5.6</v>
       </c>
-      <c r="I8" t="n">
+      <c r="BI8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>6.8</v>
       </c>
-      <c r="J8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU8" t="n">
         <v>5</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X8" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="BV8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="CA8" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>6.2</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,207 +2621,207 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.91</v>
       </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="T9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.08</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.79</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="X9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
         <v>11</v>
       </c>
-      <c r="Y9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AW9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG9" t="n">
         <v>7.4</v>
       </c>
-      <c r="AC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>8</v>
-      </c>
       <c r="BH9" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>6.2</v>
@@ -2830,42 +2830,42 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,225 +2875,225 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.98</v>
+        <v>1.54</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>1.84</v>
+        <v>2.68</v>
       </c>
       <c r="X10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB10" t="n">
         <v>13</v>
       </c>
-      <c r="Y10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="BC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BK10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN10" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="BO10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE10" t="n">
+      <c r="BQ10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU10" t="n">
         <v>5</v>
       </c>
-      <c r="BF10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BV10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
         <v>8.4</v>
@@ -3102,24 +3102,24 @@
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I11" t="n">
         <v>5.1</v>
       </c>
-      <c r="I11" t="n">
-        <v>8.4</v>
-      </c>
       <c r="J11" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="O11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM11" t="n">
         <v>180</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>300</v>
-      </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO11" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.72</v>
+        <v>6.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.15</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO11" t="n">
         <v>3.7</v>
       </c>
-      <c r="BC11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>2.92</v>
-      </c>
       <c r="BP11" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,1006 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="G12" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.55</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>1.43</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
         <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF12" t="n">
         <v>11.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AM12" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>11.5</v>
       </c>
-      <c r="BG12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11</v>
-      </c>
       <c r="BK12" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN12" t="n">
         <v>4.6</v>
       </c>
       <c r="BO12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:44:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Brusque FC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:44:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC14" t="n">
         <v>3.85</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BD14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:44:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP15" t="n">
         <v>14</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR12" t="n">
+      <c r="BQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR15" t="n">
         <v>32</v>
       </c>
-      <c r="BS12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT12" t="n">
+      <c r="BS15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT15" t="n">
         <v>8.6</v>
       </c>
-      <c r="BU12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV12" t="n">
+      <c r="BU15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV15" t="n">
         <v>48</v>
       </c>
-      <c r="BW12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
+      <c r="BW15" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>29</v>
       </c>
-      <c r="CA12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-07-05 07:32:29</t>
+      <c r="CA15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -875,34 +875,34 @@
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
@@ -911,7 +911,7 @@
         <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
         <v>12.5</v>
@@ -920,7 +920,7 @@
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
         <v>10.5</v>
@@ -947,13 +947,13 @@
         <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
         <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
@@ -968,55 +968,55 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB2" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC2" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
@@ -1028,13 +1028,13 @@
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
@@ -1046,16 +1046,16 @@
         <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU2" t="n">
         <v>5</v>
@@ -1064,13 +1064,13 @@
         <v>28</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
         <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="G3" t="n">
         <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1150,7 +1150,7 @@
         <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
         <v>1.03</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1404,7 +1404,7 @@
         <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
@@ -1416,7 +1416,7 @@
         <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X4" t="n">
         <v>32</v>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>13.5</v>
@@ -1446,7 +1446,7 @@
         <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
         <v>15</v>
@@ -1470,19 +1470,19 @@
         <v>13.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>14.5</v>
@@ -1506,19 +1506,19 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
@@ -1646,7 +1646,7 @@
         <v>3.95</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
@@ -1667,10 +1667,10 @@
         <v>2.24</v>
       </c>
       <c r="V5" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
         <v>16</v>
@@ -1709,13 +1709,13 @@
         <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AK5" t="n">
         <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1736,7 +1736,7 @@
         <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1760,10 +1760,10 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC5" t="n">
         <v>32</v>
@@ -1775,7 +1775,7 @@
         <v>36</v>
       </c>
       <c r="BF5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG5" t="n">
         <v>15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -1885,10 +1885,10 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -2139,10 +2139,10 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2157,7 +2157,7 @@
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
@@ -2166,7 +2166,7 @@
         <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>1.94</v>
       </c>
       <c r="I8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
         <v>3.9</v>
@@ -2420,16 +2420,16 @@
         <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W8" t="n">
         <v>1.37</v>
@@ -2471,7 +2471,7 @@
         <v>27</v>
       </c>
       <c r="AJ8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="n">
         <v>36</v>
@@ -2489,7 +2489,7 @@
         <v>7.6</v>
       </c>
       <c r="AP8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>14.5</v>
@@ -2504,16 +2504,16 @@
         <v>19.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
         <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY8" t="n">
         <v>12.5</v>
@@ -2525,16 +2525,16 @@
         <v>17</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF8" t="n">
         <v>12</v>
@@ -2588,7 +2588,7 @@
         <v>13.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.7</v>
+        <v>9.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -2635,70 +2635,70 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="H9" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB9" t="n">
         <v>11.5</v>
@@ -2713,7 +2713,7 @@
         <v>36</v>
       </c>
       <c r="AF9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
@@ -2731,34 +2731,34 @@
         <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
         <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
         <v>11</v>
@@ -2767,43 +2767,43 @@
         <v>29</v>
       </c>
       <c r="AX9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB9" t="n">
         <v>34</v>
       </c>
-      <c r="BB9" t="n">
-        <v>28</v>
-      </c>
       <c r="BC9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
         <v>4.8</v>
@@ -2812,19 +2812,19 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2833,22 +2833,22 @@
         <v>7.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW9" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -2916,13 +2916,13 @@
         <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
         <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
@@ -2940,7 +2940,7 @@
         <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="X10" t="n">
         <v>25</v>
@@ -3054,7 +3054,7 @@
         <v>4.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
         <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
         <v>3.2</v>
@@ -3170,13 +3170,13 @@
         <v>2.84</v>
       </c>
       <c r="O11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
         <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R11" t="n">
         <v>1.23</v>
@@ -3209,7 +3209,7 @@
         <v>130</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7.8</v>
@@ -3257,10 +3257,10 @@
         <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT11" t="n">
         <v>6.4</v>
@@ -3269,10 +3269,10 @@
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3281,46 +3281,46 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH11" t="n">
         <v>2.96</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BN11" t="n">
         <v>4.6</v>
@@ -3332,41 +3332,41 @@
         <v>16.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
         <v>7.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.93</v>
       </c>
       <c r="G12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H12" t="n">
         <v>4.7</v>
@@ -3421,7 +3421,7 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O12" t="n">
         <v>1.46</v>
@@ -3430,7 +3430,7 @@
         <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R12" t="n">
         <v>1.22</v>
@@ -3448,16 +3448,16 @@
         <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X12" t="n">
         <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA12" t="n">
         <v>160</v>
@@ -3469,7 +3469,7 @@
         <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
         <v>85</v>
@@ -3481,7 +3481,7 @@
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
         <v>120</v>
@@ -3514,7 +3514,7 @@
         <v>30</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
         <v>6</v>
@@ -3526,7 +3526,7 @@
         <v>17.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
         <v>9.199999999999999</v>
@@ -3538,7 +3538,7 @@
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
         <v>19</v>
@@ -3547,16 +3547,16 @@
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
         <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH12" t="n">
         <v>3</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
         <v>16</v>
       </c>
       <c r="Z13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
         <v>120</v>
@@ -3738,19 +3738,19 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
         <v>24</v>
@@ -3759,58 +3759,58 @@
         <v>85</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.6</v>
+        <v>3.9</v>
       </c>
       <c r="AQ13" t="n">
         <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.4</v>
+        <v>3.95</v>
       </c>
       <c r="AY13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH13" t="n">
         <v>3.15</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -3905,166 +3905,166 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="P14" t="n">
         <v>1.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.42</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
         <v>2.92</v>
@@ -4100,7 +4100,7 @@
         <v>42</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="BT14" t="n">
         <v>10.5</v>
@@ -4109,7 +4109,7 @@
         <v>4.8</v>
       </c>
       <c r="BV14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
         <v>2.14</v>
@@ -4124,11 +4124,11 @@
         <v>38</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.2</v>
+        <v>2.08</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H15" t="n">
         <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.55</v>
@@ -4330,7 +4330,7 @@
         <v>11</v>
       </c>
       <c r="BK15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4342,7 +4342,7 @@
         <v>4.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BP15" t="n">
         <v>14</v>
@@ -4360,7 +4360,7 @@
         <v>8.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV15" t="n">
         <v>48</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -875,40 +875,40 @@
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
         <v>1.99</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
         <v>14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P3" t="n">
         <v>2.02</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Q3" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I4" t="n">
         <v>2.88</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>3.95</v>
@@ -1395,19 +1395,19 @@
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
         <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U4" t="n">
         <v>2.68</v>
@@ -1416,7 +1416,7 @@
         <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X4" t="n">
         <v>32</v>
@@ -1440,7 +1440,7 @@
         <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF4" t="n">
         <v>25</v>
@@ -1473,7 +1473,7 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
         <v>15.5</v>
@@ -1482,7 +1482,7 @@
         <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
         <v>14.5</v>
@@ -1506,10 +1506,10 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G5" t="n">
         <v>3.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I5" t="n">
         <v>2.38</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>3.7</v>
@@ -1652,7 +1652,7 @@
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
@@ -1697,7 +1697,7 @@
         <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG5" t="n">
         <v>14.5</v>
@@ -1709,7 +1709,7 @@
         <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="AK5" t="n">
         <v>40</v>
@@ -1730,13 +1730,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
         <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1760,7 +1760,7 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB5" t="n">
         <v>29</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1912,7 +1912,7 @@
         <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G8" t="n">
         <v>3.7</v>
       </c>
       <c r="H8" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="I8" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
@@ -2405,19 +2405,19 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.12</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
         <v>1.38</v>
       </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S8" t="n">
         <v>1.94</v>
@@ -2426,82 +2426,82 @@
         <v>1.42</v>
       </c>
       <c r="U8" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="V8" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="W8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="Y8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI8" t="n">
         <v>23</v>
       </c>
-      <c r="Z8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>27</v>
-      </c>
       <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
         <v>60</v>
       </c>
-      <c r="AK8" t="n">
-        <v>36</v>
-      </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AN8" t="n">
         <v>18.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.2</v>
+        <v>30</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT8" t="n">
         <v>20</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>19.5</v>
       </c>
       <c r="AU8" t="n">
         <v>10</v>
@@ -2510,37 +2510,37 @@
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.1</v>
+        <v>26</v>
       </c>
       <c r="AY8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.4</v>
+        <v>50</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.1</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="BF8" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="n">
         <v>5.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -2638,115 +2638,115 @@
         <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="I9" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA9" t="n">
         <v>50</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AP9" t="n">
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
@@ -2758,7 +2758,7 @@
         <v>9</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
         <v>11</v>
@@ -2788,34 +2788,34 @@
         <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>18.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO9" t="n">
         <v>4.4</v>
@@ -2824,31 +2824,31 @@
         <v>23</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU9" t="n">
         <v>4.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G10" t="n">
         <v>1.59</v>
@@ -2901,52 +2901,52 @@
         <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Z10" t="n">
         <v>55</v>
@@ -2955,28 +2955,28 @@
         <v>170</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
         <v>27</v>
       </c>
       <c r="AE10" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
         <v>17.5</v>
@@ -2988,49 +2988,49 @@
         <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT10" t="n">
         <v>7.8</v>
       </c>
-      <c r="AO10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>9</v>
       </c>
       <c r="AV10" t="n">
         <v>19.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
         <v>13</v>
@@ -3039,52 +3039,52 @@
         <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BP10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT10" t="n">
         <v>10</v>
@@ -3093,26 +3093,26 @@
         <v>5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
         <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q11" t="n">
         <v>2.38</v>
@@ -3182,7 +3182,7 @@
         <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
         <v>2.04</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>2.06</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>3.25</v>
@@ -3415,16 +3415,16 @@
         <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
         <v>1.67</v>
@@ -3439,13 +3439,13 @@
         <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
         <v>1.79</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
         <v>1.94</v>
@@ -3454,13 +3454,13 @@
         <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="n">
         <v>7.4</v>
@@ -3472,7 +3472,7 @@
         <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF12" t="n">
         <v>11.5</v>
@@ -3484,10 +3484,10 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
         <v>27</v>
@@ -3499,10 +3499,10 @@
         <v>210</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP12" t="n">
         <v>8.800000000000001</v>
@@ -3511,10 +3511,10 @@
         <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT12" t="n">
         <v>6</v>
@@ -3523,10 +3523,10 @@
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12" t="n">
         <v>9.199999999999999</v>
@@ -3547,22 +3547,22 @@
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG12" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>9</v>
       </c>
       <c r="BH12" t="n">
         <v>3</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ12" t="n">
         <v>11.5</v>
@@ -3574,16 +3574,16 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BP12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ12" t="n">
         <v>6.6</v>
@@ -3592,35 +3592,35 @@
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
         <v>8.4</v>
       </c>
-      <c r="BU12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>2.18</v>
@@ -3777,7 +3777,7 @@
         <v>3.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW13" t="n">
         <v>5.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3905,166 +3905,166 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="O14" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
         <v>1.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS14" t="n">
         <v>4.4</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="n">
         <v>2.92</v>
@@ -4100,7 +4100,7 @@
         <v>42</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
         <v>10.5</v>
@@ -4124,11 +4124,11 @@
         <v>38</v>
       </c>
       <c r="CA14" t="n">
-        <v>2.08</v>
+        <v>7.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
         <v>4.7</v>
@@ -4174,7 +4174,7 @@
         <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -4192,7 +4192,7 @@
         <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
@@ -4216,7 +4216,7 @@
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z15" t="n">
         <v>40</v>
@@ -4252,7 +4252,7 @@
         <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>44</v>
@@ -4282,7 +4282,7 @@
         <v>6.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
         <v>17</v>
@@ -4291,7 +4291,7 @@
         <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY15" t="n">
         <v>8.800000000000001</v>
@@ -4303,7 +4303,7 @@
         <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
         <v>18</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
         <v>2.62</v>
@@ -890,13 +890,13 @@
         <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.77</v>
@@ -920,7 +920,7 @@
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
         <v>10.5</v>
@@ -977,7 +977,7 @@
         <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>6</v>
@@ -1007,7 +1007,7 @@
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
         <v>8.4</v>
@@ -1028,49 +1028,49 @@
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV2" t="n">
         <v>28</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
@@ -1141,10 +1141,10 @@
         <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
@@ -1153,10 +1153,10 @@
         <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
         <v>1.21</v>
@@ -1168,7 +1168,7 @@
         <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>44</v>
@@ -1177,10 +1177,10 @@
         <v>160</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
@@ -1189,10 +1189,10 @@
         <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>21</v>
@@ -1201,10 +1201,10 @@
         <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL3" t="n">
         <v>36</v>
@@ -1213,7 +1213,7 @@
         <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
         <v>80</v>
@@ -1222,13 +1222,13 @@
         <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.9</v>
+        <v>2.44</v>
       </c>
       <c r="AT3" t="n">
         <v>7.2</v>
@@ -1240,7 +1240,7 @@
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
         <v>8</v>
@@ -1252,7 +1252,7 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
         <v>13</v>
@@ -1261,22 +1261,22 @@
         <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.9</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
         <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="n">
         <v>3.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>2.74</v>
       </c>
       <c r="I4" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J4" t="n">
         <v>3.8</v>
@@ -1410,10 +1410,10 @@
         <v>1.52</v>
       </c>
       <c r="U4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
         <v>1.61</v>
@@ -1473,7 +1473,7 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>15.5</v>
@@ -1482,7 +1482,7 @@
         <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>14.5</v>
@@ -1506,10 +1506,10 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
         <v>2.38</v>
@@ -1634,7 +1634,7 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>1.39</v>
@@ -1652,25 +1652,25 @@
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
         <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
         <v>16</v>
@@ -1697,7 +1697,7 @@
         <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
         <v>14.5</v>
@@ -1709,7 +1709,7 @@
         <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>540</v>
+        <v>830</v>
       </c>
       <c r="AK5" t="n">
         <v>40</v>
@@ -1730,13 +1730,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
         <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1757,13 +1757,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
         <v>26</v>
       </c>
       <c r="BB5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC5" t="n">
         <v>32</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q6" t="n">
         <v>1.01</v>
@@ -1912,7 +1912,7 @@
         <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
@@ -2118,22 +2118,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Mercedes</t>
+          <t>Deportivo Espanol</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2142,7 +2142,7 @@
         <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
@@ -2166,7 +2166,7 @@
         <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2343,21 +2343,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Club Mercedes</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.96</v>
+        <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>7.4</v>
+        <v>1.08</v>
       </c>
       <c r="O8" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>1.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.89</v>
+        <v>1.08</v>
       </c>
       <c r="S8" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.68</v>
+        <v>1.96</v>
       </c>
       <c r="I9" t="n">
-        <v>2.96</v>
+        <v>2.06</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="O9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.39</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.12</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>1.96</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>1.94</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD9" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AE9" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AF9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB9" t="n">
         <v>50</v>
       </c>
-      <c r="AB9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="BC9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="BK9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BW9" t="n">
         <v>9.6</v>
       </c>
-      <c r="BN9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.55</v>
+        <v>2.52</v>
       </c>
       <c r="G10" t="n">
-        <v>1.59</v>
+        <v>2.66</v>
       </c>
       <c r="H10" t="n">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>27</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA10" t="n">
         <v>55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>170</v>
       </c>
       <c r="AB10" t="n">
         <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
         <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AP10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR10" t="n">
         <v>16</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AS10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>6.8</v>
       </c>
-      <c r="AT10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.83</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>1.86</v>
+        <v>2.68</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AA11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM11" t="n">
         <v>130</v>
       </c>
-      <c r="AB11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>180</v>
-      </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>9.6</v>
       </c>
       <c r="AO11" t="n">
         <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AX11" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS11" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA11" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
@@ -3388,79 +3388,79 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="O12" t="n">
         <v>1.47</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T12" t="n">
         <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
         <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA12" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB12" t="n">
         <v>7.4</v>
@@ -3469,165 +3469,165 @@
         <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN12" t="n">
         <v>26</v>
       </c>
-      <c r="AK12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>22</v>
-      </c>
       <c r="AO12" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BA12" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>19</v>
+        <v>5.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BP12" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BT12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.47</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.26</v>
       </c>
-      <c r="S13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.27</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB13" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
         <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AJ13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10</v>
-      </c>
       <c r="BN13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BP13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ13" t="n">
         <v>6.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BT13" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BU13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV13" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
@@ -3891,498 +3891,752 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>5.1</v>
       </c>
-      <c r="I14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="BA14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO14" t="n">
         <v>3.9</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="BP14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>7.2</v>
       </c>
-      <c r="AC14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="BR14" t="n">
         <v>36</v>
       </c>
-      <c r="AI14" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>320</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ14" t="n">
+      <c r="BS14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU14" t="n">
         <v>5.5</v>
       </c>
-      <c r="BR14" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.14</v>
+        <v>9</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-05 16:12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Tecnico Universitario</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="F16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN16" t="n">
         <v>4.7</v>
       </c>
-      <c r="I15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="BO16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL15" t="n">
+      <c r="BT16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV16" t="n">
         <v>44</v>
       </c>
-      <c r="AM15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="BW16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG15" t="n">
+      <c r="BZ16" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BH15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>29</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>2026-07-05 14:04:08</t>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G2" t="n">
         <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>3.5</v>
@@ -887,7 +887,7 @@
         <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
@@ -956,7 +956,7 @@
         <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>24</v>
@@ -974,7 +974,7 @@
         <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.69</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
@@ -1135,19 +1135,19 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
         <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
         <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
         <v>3.05</v>
@@ -1156,25 +1156,25 @@
         <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
         <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AA3" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
         <v>9.6</v>
@@ -1183,22 +1183,22 @@
         <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AJ3" t="n">
         <v>970</v>
@@ -1207,28 +1207,28 @@
         <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AO3" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AP3" t="n">
         <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
         <v>7.2</v>
@@ -1240,7 +1240,7 @@
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>8</v>
@@ -1252,7 +1252,7 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
         <v>13</v>
@@ -1261,16 +1261,16 @@
         <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
         <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.75</v>
@@ -1300,7 +1300,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>9</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1324,7 +1324,7 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.23</v>
@@ -1392,7 +1392,7 @@
         <v>5.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
         <v>2.58</v>
@@ -1404,7 +1404,7 @@
         <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
         <v>1.52</v>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>13.5</v>
@@ -1473,16 +1473,16 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>15.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
         <v>14.5</v>
@@ -1506,19 +1506,19 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H5" t="n">
         <v>2.26</v>
@@ -1643,7 +1643,7 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
@@ -1652,7 +1652,7 @@
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
@@ -1661,7 +1661,7 @@
         <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
         <v>2.26</v>
@@ -1670,7 +1670,7 @@
         <v>1.73</v>
       </c>
       <c r="W5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
         <v>16</v>
@@ -1709,7 +1709,7 @@
         <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>830</v>
+        <v>120</v>
       </c>
       <c r="AK5" t="n">
         <v>40</v>
@@ -1718,7 +1718,7 @@
         <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN5" t="n">
         <v>36</v>
@@ -1730,7 +1730,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
         <v>13.5</v>
@@ -1739,7 +1739,7 @@
         <v>19</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7.4</v>
@@ -1760,7 +1760,7 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>30</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.81</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>2.42</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1909,7 +1909,7 @@
         <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S6" t="n">
         <v>1.52</v>
@@ -1921,118 +1921,118 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>2.26</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2157,16 +2157,16 @@
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2175,118 +2175,118 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>2.56</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q8" t="n">
         <v>1.01</v>
@@ -2420,127 +2420,127 @@
         <v>1.08</v>
       </c>
       <c r="S8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BG8" t="n">
         <v>1.55</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>2.06</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -2686,7 +2686,7 @@
         <v>1.94</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
         <v>100</v>
@@ -2698,10 +2698,10 @@
         <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AB9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AC9" t="n">
         <v>13</v>
@@ -2716,7 +2716,7 @@
         <v>75</v>
       </c>
       <c r="AG9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH9" t="n">
         <v>15</v>
@@ -2725,7 +2725,7 @@
         <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AK9" t="n">
         <v>60</v>
@@ -2761,16 +2761,16 @@
         <v>10</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AW9" t="n">
         <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AY9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>12</v>
@@ -2779,7 +2779,7 @@
         <v>15.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BC9" t="n">
         <v>21</v>
@@ -2791,7 +2791,7 @@
         <v>24</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG9" t="n">
         <v>6.4</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN9" t="n">
         <v>8</v>
@@ -2821,25 +2821,25 @@
         <v>6</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BW9" t="n">
         <v>9.6</v>
@@ -2848,17 +2848,17 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>11.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
@@ -2904,7 +2904,7 @@
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
@@ -2937,10 +2937,10 @@
         <v>1.93</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
@@ -2979,13 +2979,13 @@
         <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="AM10" t="n">
         <v>130</v>
@@ -3009,13 +3009,13 @@
         <v>38</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW10" t="n">
         <v>29</v>
@@ -3027,13 +3027,13 @@
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
         <v>36</v>
       </c>
       <c r="BB10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC10" t="n">
         <v>26</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
         <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="X11" t="n">
         <v>22</v>
@@ -3206,7 +3206,7 @@
         <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB11" t="n">
         <v>9.6</v>
@@ -3215,7 +3215,7 @@
         <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
         <v>100</v>
@@ -3242,7 +3242,7 @@
         <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>9.6</v>
@@ -3257,10 +3257,10 @@
         <v>18.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -3272,7 +3272,7 @@
         <v>19.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX11" t="n">
         <v>8.6</v>
@@ -3284,7 +3284,7 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
         <v>13</v>
@@ -3293,7 +3293,7 @@
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BE11" t="n">
         <v>7</v>
@@ -3308,7 +3308,7 @@
         <v>3.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
         <v>1.44</v>
@@ -3421,7 +3421,7 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O12" t="n">
         <v>1.47</v>
@@ -3445,7 +3445,7 @@
         <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
         <v>1.87</v>
@@ -3460,7 +3460,7 @@
         <v>38</v>
       </c>
       <c r="AA12" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>7.4</v>
@@ -3472,19 +3472,19 @@
         <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AF12" t="n">
         <v>13.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
         <v>26</v>
       </c>
       <c r="AI12" t="n">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="AJ12" t="n">
         <v>32</v>
@@ -3496,13 +3496,13 @@
         <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>26</v>
       </c>
       <c r="AO12" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
         <v>9</v>
@@ -3511,10 +3511,10 @@
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
@@ -3523,40 +3523,40 @@
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
         <v>17</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH12" t="n">
         <v>2.96</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -3657,10 +3657,10 @@
         <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.25</v>
@@ -3705,16 +3705,16 @@
         <v>1.94</v>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
         <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AA13" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>7.4</v>
@@ -3723,10 +3723,10 @@
         <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
         <v>11.5</v>
@@ -3738,10 +3738,10 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>110</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>26</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -3750,13 +3750,13 @@
         <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
         <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
         <v>8.800000000000001</v>
@@ -3765,10 +3765,10 @@
         <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
@@ -3780,7 +3780,7 @@
         <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
         <v>9.199999999999999</v>
@@ -3792,7 +3792,7 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB13" t="n">
         <v>19</v>
@@ -3801,16 +3801,16 @@
         <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
         <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH13" t="n">
         <v>2.98</v>
@@ -3822,7 +3822,7 @@
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,10 +3834,10 @@
         <v>4.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ13" t="n">
         <v>6.6</v>
@@ -3849,7 +3849,7 @@
         <v>8.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU13" t="n">
         <v>5.8</v>
@@ -3864,17 +3864,17 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -3908,22 +3908,22 @@
         <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H14" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3935,136 +3935,136 @@
         <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q14" t="n">
         <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>4.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA14" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>9</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="n">
         <v>14</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>370</v>
       </c>
       <c r="AJ14" t="n">
         <v>34</v>
       </c>
       <c r="AK14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
         <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AV14" t="n">
         <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD14" t="n">
         <v>29</v>
       </c>
       <c r="BE14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF14" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF14" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG14" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BH14" t="n">
         <v>3.15</v>
@@ -4091,7 +4091,7 @@
         <v>3.9</v>
       </c>
       <c r="BP14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ14" t="n">
         <v>7.2</v>
@@ -4106,7 +4106,7 @@
         <v>7.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV14" t="n">
         <v>36</v>
@@ -4118,7 +4118,7 @@
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.67</v>
       </c>
       <c r="G15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H15" t="n">
         <v>5.3</v>
@@ -4219,7 +4219,7 @@
         <v>19</v>
       </c>
       <c r="Z15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA15" t="n">
         <v>290</v>
@@ -4255,7 +4255,7 @@
         <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
         <v>300</v>
@@ -4318,7 +4318,7 @@
         <v>3.7</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH15" t="n">
         <v>2.92</v>
@@ -4363,7 +4363,7 @@
         <v>4.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW15" t="n">
         <v>2.14</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,234 +843,234 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>00:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>AV Alta FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Charlotte Independence</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I2" t="n">
         <v>2.34</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE2" t="n">
         <v>24</v>
       </c>
-      <c r="AA2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>42</v>
-      </c>
       <c r="AF2" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
         <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
         <v>17</v>
       </c>
-      <c r="AS2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AX2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY2" t="n">
         <v>12</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AZ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>9</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB2" t="n">
+      <c r="BK2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BN2" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BO2" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BX2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SK Super Nova</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.69</v>
+        <v>2.34</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.4</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W3" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>700</v>
+        <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>36</v>
       </c>
-      <c r="AI3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>970</v>
-      </c>
       <c r="AK3" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>700</v>
+        <v>42</v>
       </c>
       <c r="AP3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX3" t="n">
         <v>12</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BR3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS3" t="n">
         <v>8</v>
       </c>
-      <c r="AY3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA3" t="n">
+      <c r="BT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV3" t="n">
         <v>28</v>
       </c>
-      <c r="BB3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF3" t="n">
+      <c r="BW3" t="n">
         <v>7.6</v>
       </c>
-      <c r="BG3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>9</v>
-      </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.05</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,244 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hacken</t>
+          <t>SK Super Nova</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgardens</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="H4" t="n">
-        <v>2.74</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>2.84</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR4" t="n">
         <v>18</v>
       </c>
-      <c r="Z4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AS4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA4" t="n">
         <v>28</v>
       </c>
-      <c r="AF4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO4" t="n">
+      <c r="BB4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD4" t="n">
         <v>16</v>
       </c>
-      <c r="AP4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BE4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF4" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
         <v>13.5</v>
       </c>
       <c r="BH4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN4" t="n">
         <v>4.5</v>
       </c>
-      <c r="BI4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>6</v>
-      </c>
       <c r="BO4" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.4</v>
+        <v>3.05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgardens</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="I5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.38</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AF5" t="n">
         <v>25</v>
       </c>
       <c r="AG5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AU5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP5" t="n">
         <v>17</v>
       </c>
-      <c r="AI5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>26</v>
-      </c>
       <c r="BQ5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BS5" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BW5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CSD Yupanqui</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.81</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="J6" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.09</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.52</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="W6" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="AB6" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.35</v>
+        <v>22</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.55</v>
+        <v>15</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
@@ -2118,70 +2118,70 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CSD Muniz</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportivo Espanol</t>
+          <t>CSD Yupanqui</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>110</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P7" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
         <v>500</v>
@@ -2190,13 +2190,13 @@
         <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>500</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>500</v>
@@ -2205,10 +2205,10 @@
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>500</v>
@@ -2217,7 +2217,7 @@
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -2235,64 +2235,64 @@
         <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.55</v>
+        <v>5.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
@@ -2307,7 +2307,7 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
@@ -2372,184 +2372,184 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CSR Espanol BA</t>
+          <t>CSD Muniz</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Mercedes</t>
+          <t>Deportivo Espanol</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.59</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H8" t="n">
-        <v>3.35</v>
+        <v>2.72</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J8" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>1.86</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="Q8" t="n">
         <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.56</v>
+        <v>7.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>95</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.55</v>
+        <v>5.7</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK8" t="n">
         <v>1.01</v>
@@ -2561,13 +2561,13 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO8" t="n">
         <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.01</v>
@@ -2579,13 +2579,13 @@
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU8" t="n">
         <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
@@ -2597,21 +2597,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Club Mercedes</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.45</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.7</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S9" t="n">
         <v>1.02</v>
       </c>
-      <c r="N9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.96</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>3.15</v>
+        <v>1.61</v>
       </c>
       <c r="V9" t="n">
-        <v>1.94</v>
+        <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="X9" t="n">
-        <v>100</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN9" t="n">
         <v>28</v>
       </c>
-      <c r="AB9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AO9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP9" t="n">
         <v>17.5</v>
       </c>
-      <c r="AH9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>490</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>1.95</v>
       </c>
       <c r="I10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U10" t="n">
         <v>3.1</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.93</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>18.5</v>
       </c>
       <c r="AF10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>17</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AR10" t="n">
         <v>16</v>
       </c>
       <c r="AS10" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>8.6</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BK10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>7</v>
       </c>
-      <c r="AV10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC10" t="n">
+      <c r="BR10" t="n">
         <v>26</v>
       </c>
-      <c r="BD10" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
       <c r="BS10" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BU10" t="n">
         <v>4.9</v>
       </c>
       <c r="BV10" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
-        <v>5.9</v>
+        <v>2.64</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K11" t="n">
         <v>4.2</v>
       </c>
-      <c r="K11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>27</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17.5</v>
+        <v>130</v>
       </c>
       <c r="AK11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>18</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="BA11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB11" t="n">
         <v>34</v>
       </c>
-      <c r="AM11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS11" t="n">
+      <c r="BC11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY11" t="n">
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BT11" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,244 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.9</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="Z12" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE12" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>370</v>
+        <v>95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>26</v>
+        <v>8.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD12" t="n">
+      <c r="BN12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU12" t="n">
         <v>5.6</v>
       </c>
-      <c r="BE12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA12" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
@@ -3642,76 +3642,76 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
         <v>4.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T13" t="n">
         <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
@@ -3723,165 +3723,165 @@
         <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AJ13" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AO13" t="n">
         <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BG13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BJ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>9</v>
-      </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,239 +3896,239 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="H14" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="P14" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
         <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG14" t="n">
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
         <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ14" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG14" t="n">
+      <c r="BK14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ14" t="n">
+      <c r="BN14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
@@ -4145,498 +4145,752 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="n">
-        <v>8.4</v>
+        <v>3.95</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="P15" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="U15" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
         <v>11.5</v>
       </c>
       <c r="Y15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP15" t="n">
         <v>19</v>
       </c>
-      <c r="Z15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH15" t="n">
+      <c r="BQ15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR15" t="n">
         <v>36</v>
       </c>
-      <c r="AI15" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>320</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>42</v>
-      </c>
       <c r="BS15" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV15" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.14</v>
+        <v>9</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-05 20:28:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Tecnico Universitario</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="F17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.8</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>1.91</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1.92</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="V17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X17" t="n">
         <v>13</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y17" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z17" t="n">
         <v>36</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA17" t="n">
         <v>130</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK17" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>11</v>
       </c>
-      <c r="AH16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL16" t="n">
+      <c r="BR17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV17" t="n">
         <v>44</v>
       </c>
-      <c r="AM16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BW17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA16" t="n">
+      <c r="BZ17" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA17" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-07-05 18:20:14</t>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
         <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.28</v>
@@ -881,37 +881,37 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
         <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
         <v>17</v>
@@ -923,13 +923,13 @@
         <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -938,7 +938,7 @@
         <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
         <v>17.5</v>
@@ -953,13 +953,13 @@
         <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
         <v>12.5</v>
@@ -971,106 +971,106 @@
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS2" t="n">
         <v>23</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ2" t="n">
         <v>16.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
         <v>20</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
         <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
         <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -1156,7 +1156,7 @@
         <v>1.77</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
         <v>1.4</v>
@@ -1228,7 +1228,7 @@
         <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AT3" t="n">
         <v>8.6</v>
@@ -1240,7 +1240,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
@@ -1255,7 +1255,7 @@
         <v>36</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC3" t="n">
         <v>21</v>
@@ -1264,7 +1264,7 @@
         <v>7.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
         <v>17.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
         <v>1.84</v>
@@ -1377,7 +1377,7 @@
         <v>5.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
         <v>4.4</v>
@@ -1395,7 +1395,7 @@
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
         <v>1.81</v>
@@ -1410,7 +1410,7 @@
         <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1467,7 +1467,7 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
@@ -1494,7 +1494,7 @@
         <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX4" t="n">
         <v>8</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G5" t="n">
         <v>2.62</v>
@@ -1631,7 +1631,7 @@
         <v>2.84</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
@@ -1646,25 +1646,25 @@
         <v>5.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
         <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
         <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T5" t="n">
         <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V5" t="n">
         <v>1.54</v>
@@ -1673,7 +1673,7 @@
         <v>1.61</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y5" t="n">
         <v>18</v>
@@ -1685,37 +1685,37 @@
         <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
         <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
         <v>44</v>
       </c>
       <c r="AK5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM5" t="n">
         <v>65</v>
@@ -1727,16 +1727,16 @@
         <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
         <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="AT5" t="n">
         <v>14.5</v>
@@ -1748,7 +1748,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1760,25 +1760,25 @@
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BF5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH5" t="n">
         <v>4.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
         <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
         <v>1.72</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -2208,7 +2208,7 @@
         <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH7" t="n">
         <v>500</v>
@@ -2286,7 +2286,7 @@
         <v>5.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.76</v>
@@ -2298,59 +2298,59 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BN7" t="n">
         <v>5.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>1.75</v>
       </c>
       <c r="P8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
         <v>1.01</v>
@@ -2489,10 +2489,10 @@
         <v>120</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AR8" t="n">
         <v>4.6</v>
@@ -2504,7 +2504,7 @@
         <v>3.45</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AV8" t="n">
         <v>4.5</v>
@@ -2552,59 +2552,59 @@
         <v>15</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BN8" t="n">
         <v>6.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP8" t="n">
         <v>40</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV8" t="n">
         <v>38</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -2806,49 +2806,49 @@
         <v>13.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BN9" t="n">
         <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="BP9" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT9" t="n">
         <v>9.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
         <v>1.89</v>
       </c>
       <c r="S10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="T10" t="n">
         <v>1.42</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I11" t="n">
         <v>2.94</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.46</v>
@@ -3194,10 +3194,10 @@
         <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
         <v>9.800000000000001</v>
@@ -3221,7 +3221,7 @@
         <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
@@ -3239,7 +3239,7 @@
         <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM11" t="n">
         <v>130</v>
@@ -3248,7 +3248,7 @@
         <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
         <v>11</v>
@@ -3296,13 +3296,13 @@
         <v>38</v>
       </c>
       <c r="BE11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF11" t="n">
         <v>23</v>
       </c>
       <c r="BG11" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BH11" t="n">
         <v>3.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G12" t="n">
         <v>1.61</v>
@@ -3406,10 +3406,10 @@
         <v>5.9</v>
       </c>
       <c r="I12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
         <v>4.8</v>
@@ -3427,7 +3427,7 @@
         <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
         <v>1.75</v>
@@ -3556,7 +3556,7 @@
         <v>7</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12" t="n">
         <v>3.85</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -3702,7 +3702,7 @@
         <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -3908,10 +3908,10 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
         <v>4.9</v>
@@ -3932,31 +3932,31 @@
         <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="R14" t="n">
         <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T14" t="n">
         <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
         <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X14" t="n">
         <v>10.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
@@ -4168,13 +4168,13 @@
         <v>3.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.47</v>
@@ -4183,7 +4183,7 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
         <v>1.41</v>
@@ -4201,7 +4201,7 @@
         <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
         <v>1.96</v>
@@ -4288,7 +4288,7 @@
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>6.4</v>
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,498 +4399,752 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Ivinhema FC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Asa AL</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.67</v>
+        <v>4.1</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>5.3</v>
+        <v>1.98</v>
       </c>
       <c r="I16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV16" t="n">
         <v>8.4</v>
       </c>
-      <c r="J16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>320</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS16" t="n">
+      <c r="AW16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB16" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW16" t="n">
+      <c r="BC16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD16" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
         <v>4.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.92</v>
+        <v>4.7</v>
       </c>
       <c r="BP16" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.5</v>
+        <v>2.12</v>
       </c>
       <c r="BR16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.4</v>
+        <v>2.16</v>
       </c>
       <c r="BT16" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.14</v>
+        <v>6.8</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BZ16" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-07-05 22:35:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Tecnico Universitario</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>1.81</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="G18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.5</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>4.1</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="L18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M18" t="n">
         <v>1.08</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N18" t="n">
         <v>3.2</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O18" t="n">
         <v>1.36</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="P18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2.06</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>1.29</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>3.8</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="T18" t="n">
         <v>1.92</v>
       </c>
-      <c r="V17" t="n">
+      <c r="U18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.23</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="W18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X18" t="n">
         <v>13</v>
       </c>
-      <c r="Y17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="Y18" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA18" t="n">
         <v>130</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB18" t="n">
         <v>8</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AZ18" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP17" t="n">
+      <c r="BN18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW18" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE17" t="n">
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>10</v>
       </c>
-      <c r="BF17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-07-05 20:28:02</t>
+      <c r="BZ18" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="I2" t="n">
-        <v>2.32</v>
+        <v>1.64</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="T2" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="U2" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="V2" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AF2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
         <v>12.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AY2" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
         <v>21</v>
       </c>
       <c r="BB2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC2" t="n">
         <v>34</v>
       </c>
-      <c r="BC2" t="n">
-        <v>24</v>
-      </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="BG2" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BK2" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="BM2" t="n">
-        <v>36</v>
+        <v>4.4</v>
       </c>
       <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>90</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW2" t="n">
         <v>7.2</v>
       </c>
-      <c r="BO2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BX2" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="BY2" t="n">
-        <v>16</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
         <v>3.5</v>
       </c>
       <c r="J3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -1135,25 +1135,25 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
         <v>2.08</v>
@@ -1168,16 +1168,16 @@
         <v>14</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
         <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
@@ -1189,7 +1189,7 @@
         <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
         <v>12.5</v>
@@ -1201,7 +1201,7 @@
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK3" t="n">
         <v>29</v>
@@ -1213,7 +1213,7 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
         <v>42</v>
@@ -1222,7 +1222,7 @@
         <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>17</v>
@@ -1237,16 +1237,16 @@
         <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>13.5</v>
@@ -1255,22 +1255,22 @@
         <v>36</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
         <v>21</v>
       </c>
       <c r="BD3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE3" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE3" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF3" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
@@ -1300,7 +1300,7 @@
         <v>19.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BR3" t="n">
         <v>34</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
@@ -1377,10 +1377,10 @@
         <v>5.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.36</v>
@@ -1389,25 +1389,25 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
         <v>2.06</v>
@@ -1416,13 +1416,13 @@
         <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
         <v>140</v>
@@ -1431,10 +1431,10 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC4" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
         <v>500</v>
@@ -1443,10 +1443,10 @@
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
         <v>36</v>
@@ -1455,73 +1455,73 @@
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>15</v>
-      </c>
       <c r="AW4" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD4" t="n">
         <v>8</v>
       </c>
-      <c r="AY4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>16</v>
-      </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4" t="n">
         <v>13.5</v>
@@ -1530,10 +1530,10 @@
         <v>3.75</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
         <v>5.4</v>
@@ -1548,10 +1548,10 @@
         <v>4.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ4" t="n">
         <v>5.8</v>
@@ -1575,20 +1575,20 @@
         <v>9</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.05</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA4" t="n">
         <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
         <v>2.62</v>
@@ -1634,7 +1634,7 @@
         <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.28</v>
@@ -1643,28 +1643,28 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="V5" t="n">
         <v>1.54</v>
@@ -1676,28 +1676,28 @@
         <v>29</v>
       </c>
       <c r="Y5" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB5" t="n">
         <v>18</v>
       </c>
-      <c r="Z5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>17</v>
-      </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
@@ -1706,40 +1706,40 @@
         <v>14.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL5" t="n">
         <v>44</v>
       </c>
-      <c r="AK5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>34</v>
-      </c>
       <c r="AM5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
         <v>13.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AT5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU5" t="n">
         <v>8.6</v>
@@ -1748,10 +1748,10 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
         <v>11</v>
@@ -1760,25 +1760,25 @@
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BF5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="n">
         <v>4.5</v>
@@ -1787,19 +1787,19 @@
         <v>4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
         <v>5.3</v>
@@ -1808,7 +1808,7 @@
         <v>17</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BR5" t="n">
         <v>24</v>
@@ -1823,10 +1823,10 @@
         <v>5.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>15.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -1876,22 +1876,22 @@
         <v>3.35</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1906,13 +1906,13 @@
         <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
         <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
         <v>1.73</v>
@@ -1921,7 +1921,7 @@
         <v>2.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W6" t="n">
         <v>1.4</v>
@@ -1933,7 +1933,7 @@
         <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
         <v>30</v>
@@ -1960,7 +1960,7 @@
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
         <v>120</v>
@@ -1990,7 +1990,7 @@
         <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
         <v>12.5</v>
@@ -2014,22 +2014,22 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD6" t="n">
         <v>30</v>
       </c>
-      <c r="BC6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>38</v>
-      </c>
       <c r="BE6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG6" t="n">
         <v>15</v>
@@ -2038,19 +2038,19 @@
         <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
@@ -2062,41 +2062,41 @@
         <v>27</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
         <v>5.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV6" t="n">
         <v>16.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6" t="n">
         <v>29</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G7" t="n">
         <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
         <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -2151,7 +2151,7 @@
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="O7" t="n">
         <v>1.53</v>
@@ -2169,10 +2169,10 @@
         <v>5.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V7" t="n">
         <v>1.31</v>
@@ -2184,7 +2184,7 @@
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -2193,13 +2193,13 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -2235,58 +2235,58 @@
         <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.5</v>
+        <v>2.96</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY7" t="n">
         <v>5.4</v>
       </c>
-      <c r="AX7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BC7" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="BE7" t="n">
         <v>5.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.2</v>
+        <v>2.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.6</v>
+        <v>2.28</v>
       </c>
       <c r="BH7" t="n">
         <v>2.76</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>5.3</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>2.72</v>
       </c>
       <c r="I8" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
         <v>2.46</v>
@@ -2408,7 +2408,7 @@
         <v>1.86</v>
       </c>
       <c r="O8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="P8" t="n">
         <v>1.3</v>
@@ -2429,13 +2429,13 @@
         <v>1.51</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
         <v>1.37</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="Y8" t="n">
         <v>7.8</v>
@@ -2459,7 +2459,7 @@
         <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
         <v>19</v>
@@ -2492,55 +2492,55 @@
         <v>3.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="n">
         <v>2.42</v>
@@ -2564,7 +2564,7 @@
         <v>6.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BP8" t="n">
         <v>40</v>
@@ -2582,7 +2582,7 @@
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="BV8" t="n">
         <v>38</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
         <v>2.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P9" t="n">
         <v>1.46</v>
@@ -2674,7 +2674,7 @@
         <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.02</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.16</v>
@@ -2686,7 +2686,7 @@
         <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X9" t="n">
         <v>9.199999999999999</v>
@@ -2800,7 +2800,7 @@
         <v>2.84</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>13.5</v>
@@ -2818,7 +2818,7 @@
         <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
         <v>17.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I10" t="n">
         <v>2.04</v>
@@ -2922,16 +2922,16 @@
         <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R10" t="n">
         <v>1.89</v>
       </c>
       <c r="S10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U10" t="n">
         <v>3.1</v>
@@ -2940,7 +2940,7 @@
         <v>1.96</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
         <v>48</v>
@@ -2949,58 +2949,58 @@
         <v>22</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>18.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AG10" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ10" t="n">
         <v>120</v>
       </c>
       <c r="AK10" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
         <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AP10" t="n">
         <v>24</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR10" t="n">
         <v>16</v>
@@ -3009,7 +3009,7 @@
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU10" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
         <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AY10" t="n">
         <v>12.5</v>
@@ -3030,19 +3030,19 @@
         <v>11</v>
       </c>
       <c r="BA10" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BF10" t="n">
         <v>15</v>
@@ -3054,13 +3054,13 @@
         <v>5.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3072,7 +3072,7 @@
         <v>8</v>
       </c>
       <c r="BO10" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BP10" t="n">
         <v>24</v>
@@ -3081,7 +3081,7 @@
         <v>7</v>
       </c>
       <c r="BR10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
         <v>7.2</v>
@@ -3090,13 +3090,13 @@
         <v>5.9</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
         <v>13</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3108,11 +3108,11 @@
         <v>11.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H11" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
         <v>3.7</v>
@@ -3164,10 +3164,10 @@
         <v>1.46</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>1.39</v>
@@ -3194,25 +3194,25 @@
         <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
         <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
         <v>19</v>
       </c>
       <c r="AA11" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AB11" t="n">
         <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
@@ -3230,31 +3230,31 @@
         <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
         <v>120</v>
       </c>
-      <c r="AM11" t="n">
-        <v>130</v>
-      </c>
       <c r="AN11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
         <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
         <v>16</v>
@@ -3263,19 +3263,19 @@
         <v>38</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU11" t="n">
         <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
@@ -3284,25 +3284,25 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB11" t="n">
         <v>34</v>
       </c>
       <c r="BC11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BH11" t="n">
         <v>3.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G12" t="n">
         <v>1.61</v>
       </c>
       <c r="H12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>7</v>
@@ -3433,16 +3433,16 @@
         <v>1.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
         <v>1.83</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
         <v>1.16</v>
@@ -3454,7 +3454,7 @@
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z12" t="n">
         <v>55</v>
@@ -3469,10 +3469,10 @@
         <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>480</v>
       </c>
       <c r="AF12" t="n">
         <v>10.5</v>
@@ -3481,16 +3481,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="AJ12" t="n">
         <v>15.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL12" t="n">
         <v>34</v>
@@ -3499,31 +3499,31 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO12" t="n">
         <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
         <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
         <v>8.800000000000001</v>
@@ -3535,16 +3535,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD12" t="n">
         <v>16</v>
@@ -3553,22 +3553,22 @@
         <v>9</v>
       </c>
       <c r="BF12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH12" t="n">
         <v>3.85</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -3651,49 +3651,49 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
         <v>2.12</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P13" t="n">
         <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
         <v>4.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
         <v>1.9</v>
@@ -3705,13 +3705,13 @@
         <v>1.89</v>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
@@ -3723,43 +3723,43 @@
         <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AE13" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
         <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>11</v>
@@ -3768,7 +3768,7 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3777,46 +3777,46 @@
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
         <v>11.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BB13" t="n">
         <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BF13" t="n">
-        <v>17</v>
+        <v>8.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BH13" t="n">
         <v>2.96</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ13" t="n">
         <v>11</v>
@@ -3828,16 +3828,16 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN13" t="n">
         <v>4.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
         <v>8.199999999999999</v>
@@ -3846,7 +3846,7 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT13" t="n">
         <v>7.6</v>
@@ -3858,7 +3858,7 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
@@ -3870,11 +3870,11 @@
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
         <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
         <v>1.51</v>
@@ -3941,22 +3941,22 @@
         <v>2.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
         <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
         <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X14" t="n">
         <v>10.5</v>
@@ -3965,7 +3965,7 @@
         <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3974,13 +3974,13 @@
         <v>7.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AF14" t="n">
         <v>11.5</v>
@@ -3989,7 +3989,7 @@
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -4001,7 +4001,7 @@
         <v>27</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
@@ -4013,70 +4013,70 @@
         <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT14" t="n">
         <v>6</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BB14" t="n">
         <v>21</v>
       </c>
       <c r="BC14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG14" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>10.5</v>
       </c>
       <c r="BH14" t="n">
         <v>2.96</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ14" t="n">
         <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4088,13 +4088,13 @@
         <v>4.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4103,7 +4103,7 @@
         <v>9.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU14" t="n">
         <v>4.9</v>
@@ -4112,7 +4112,7 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4121,14 +4121,14 @@
         <v>10.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA14" t="n">
         <v>9.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="G15" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
@@ -4189,40 +4189,40 @@
         <v>1.41</v>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
         <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="X15" t="n">
         <v>11.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
         <v>9</v>
@@ -4237,22 +4237,22 @@
         <v>130</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>19.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL15" t="n">
         <v>110</v>
@@ -4261,46 +4261,46 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AO15" t="n">
         <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -4309,70 +4309,70 @@
         <v>11.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO15" t="n">
         <v>4.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR15" t="n">
         <v>36</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H16" t="n">
         <v>1.98</v>
       </c>
       <c r="I16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K16" t="n">
         <v>3.45</v>
@@ -4446,7 +4446,7 @@
         <v>1.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
@@ -4458,16 +4458,16 @@
         <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="W16" t="n">
         <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="n">
         <v>7.8</v>
@@ -4524,7 +4524,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AR16" t="n">
         <v>8.199999999999999</v>
@@ -4536,7 +4536,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
         <v>8.4</v>
@@ -4545,7 +4545,7 @@
         <v>21</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AY16" t="n">
         <v>15</v>
@@ -4554,22 +4554,22 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG16" t="n">
         <v>20</v>
@@ -4578,7 +4578,7 @@
         <v>2.78</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="BJ16" t="n">
         <v>12.5</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="BN16" t="n">
         <v>8.199999999999999</v>
@@ -4602,13 +4602,13 @@
         <v>55</v>
       </c>
       <c r="BQ16" t="n">
-        <v>2.12</v>
+        <v>9</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.16</v>
+        <v>9.6</v>
       </c>
       <c r="BT16" t="n">
         <v>4.7</v>
@@ -4626,7 +4626,7 @@
         <v>44</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="G17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
         <v>2.94</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
         <v>1.11</v>
@@ -4694,13 +4694,13 @@
         <v>2.38</v>
       </c>
       <c r="O17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
         <v>1.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
         <v>1.19</v>
@@ -4709,40 +4709,40 @@
         <v>4.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="AB17" t="n">
         <v>7.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AE17" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AF17" t="n">
         <v>11</v>
@@ -4751,10 +4751,10 @@
         <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI17" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ17" t="n">
         <v>23</v>
@@ -4766,76 +4766,76 @@
         <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AN17" t="n">
         <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV17" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC17" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BD17" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="BJ17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK17" t="n">
         <v>5.4</v>
@@ -4847,50 +4847,50 @@
         <v>2.18</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BP17" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BR17" t="n">
         <v>42</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
         <v>2.14</v>
       </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BZ17" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="CA17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>
@@ -4921,31 +4921,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.36</v>
@@ -4954,7 +4954,7 @@
         <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
         <v>1.29</v>
@@ -4963,43 +4963,43 @@
         <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W18" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y18" t="n">
         <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>21</v>
       </c>
       <c r="AE18" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
@@ -5017,49 +5017,49 @@
         <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO18" t="n">
         <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX18" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA18" t="n">
         <v>9.4</v>
@@ -5068,31 +5068,31 @@
         <v>17.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH18" t="n">
         <v>3.25</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ18" t="n">
         <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5101,50 +5101,50 @@
         <v>11.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ18" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BR18" t="n">
         <v>32</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ18" t="n">
         <v>29</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -857,43 +857,43 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G2" t="n">
         <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
         <v>3.6</v>
@@ -902,7 +902,7 @@
         <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
@@ -911,7 +911,7 @@
         <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
         <v>13</v>
@@ -920,13 +920,13 @@
         <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
         <v>14.5</v>
@@ -935,10 +935,10 @@
         <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>18</v>
@@ -950,7 +950,7 @@
         <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
@@ -962,13 +962,13 @@
         <v>23</v>
       </c>
       <c r="AO2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AP2" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
         <v>19</v>
@@ -977,7 +977,7 @@
         <v>42</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>6.6</v>
@@ -992,7 +992,7 @@
         <v>13.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>15</v>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF2" t="n">
         <v>19.5</v>
@@ -1019,10 +1019,10 @@
         <v>27</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
@@ -1034,10 +1034,10 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO2" t="n">
         <v>4.5</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
@@ -1064,13 +1064,13 @@
         <v>28</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="G3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
@@ -1135,37 +1135,37 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.08</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
         <v>26</v>
@@ -1177,7 +1177,7 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>9.6</v>
@@ -1186,25 +1186,25 @@
         <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>70</v>
@@ -1213,22 +1213,22 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>310</v>
       </c>
       <c r="AP3" t="n">
         <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
         <v>34</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
         <v>8.199999999999999</v>
@@ -1240,7 +1240,7 @@
         <v>17.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX3" t="n">
         <v>9.4</v>
@@ -1258,37 +1258,37 @@
         <v>15</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
         <v>25</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ3" t="n">
         <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
@@ -1297,44 +1297,44 @@
         <v>3.85</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
         <v>25</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA3" t="n">
         <v>13.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -1365,28 +1365,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I4" t="n">
         <v>2.76</v>
       </c>
-      <c r="I4" t="n">
-        <v>2.8</v>
-      </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
         <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
         <v>6.2</v>
@@ -1395,43 +1395,43 @@
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S4" t="n">
         <v>2.38</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AC4" t="n">
         <v>9.6</v>
@@ -1440,10 +1440,10 @@
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
@@ -1452,16 +1452,16 @@
         <v>14.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK4" t="n">
         <v>24</v>
       </c>
       <c r="AL4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM4" t="n">
         <v>55</v>
@@ -1470,25 +1470,25 @@
         <v>13.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP4" t="n">
         <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR4" t="n">
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
         <v>11.5</v>
@@ -1497,7 +1497,7 @@
         <v>22</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1506,25 +1506,25 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD4" t="n">
         <v>25</v>
       </c>
-      <c r="BB4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>23</v>
-      </c>
       <c r="BE4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BF4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="n">
         <v>4.5</v>
@@ -1536,13 +1536,13 @@
         <v>8.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN4" t="n">
         <v>6</v>
@@ -1551,16 +1551,16 @@
         <v>5.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>12.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
@@ -1569,26 +1569,26 @@
         <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW4" t="n">
         <v>14</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="BZ4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA4" t="n">
         <v>12</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
         <v>3.65</v>
@@ -1643,22 +1643,22 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
         <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
         <v>1.78</v>
@@ -1667,19 +1667,19 @@
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
         <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA5" t="n">
         <v>32</v>
@@ -1691,31 +1691,31 @@
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF5" t="n">
         <v>24</v>
       </c>
       <c r="AG5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
         <v>17.5</v>
       </c>
       <c r="AI5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK5" t="n">
         <v>38</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>40</v>
-      </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
         <v>95</v>
@@ -1736,46 +1736,46 @@
         <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY5" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF5" t="n">
         <v>30</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>29</v>
       </c>
       <c r="BG5" t="n">
         <v>17</v>
@@ -1784,7 +1784,7 @@
         <v>3.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
         <v>3.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
         <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.74</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.62</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1975,34 +1975,34 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
         <v>4.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AR6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV6" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AW6" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AX6" t="n">
         <v>5.2</v>
@@ -2011,10 +2011,10 @@
         <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="BB6" t="n">
         <v>6.6</v>
@@ -2023,28 +2023,28 @@
         <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.86</v>
+        <v>2.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.2</v>
+        <v>1.36</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
         <v>1.64</v>
@@ -2154,13 +2154,13 @@
         <v>1.86</v>
       </c>
       <c r="O7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="R7" t="n">
         <v>1.1</v>
@@ -2169,16 +2169,16 @@
         <v>7.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
         <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X7" t="n">
         <v>6.6</v>
@@ -2199,7 +2199,7 @@
         <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
         <v>70</v>
@@ -2214,13 +2214,13 @@
         <v>36</v>
       </c>
       <c r="AI7" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>170</v>
       </c>
       <c r="AK7" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AL7" t="n">
         <v>500</v>
@@ -2229,64 +2229,64 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU7" t="n">
         <v>3.55</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY7" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB7" t="n">
         <v>6</v>
       </c>
-      <c r="BB7" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BC7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF7" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF7" t="n">
-        <v>6</v>
-      </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
         <v>2.42</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -2381,67 +2381,67 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
         <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="X8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2450,31 +2450,31 @@
         <v>6.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2483,103 +2483,103 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AY8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BA8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD8" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="BJ8" t="n">
         <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP8" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU8" t="n">
         <v>4.2</v>
@@ -2588,13 +2588,13 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
         <v>3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I9" t="n">
         <v>2.04</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.22</v>
@@ -2659,7 +2659,7 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
@@ -2668,19 +2668,19 @@
         <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R9" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S9" t="n">
         <v>1.98</v>
       </c>
       <c r="T9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V9" t="n">
         <v>1.96</v>
@@ -2695,16 +2695,16 @@
         <v>22</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AB9" t="n">
         <v>32</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
         <v>12.5</v>
@@ -2716,7 +2716,7 @@
         <v>38</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AH9" t="n">
         <v>15</v>
@@ -2725,10 +2725,10 @@
         <v>27</v>
       </c>
       <c r="AJ9" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AK9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
         <v>34</v>
@@ -2737,70 +2737,70 @@
         <v>48</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AQ9" t="n">
         <v>16.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT9" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AU9" t="n">
         <v>10</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BC9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD9" t="n">
         <v>24</v>
       </c>
-      <c r="BD9" t="n">
-        <v>23</v>
-      </c>
       <c r="BE9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BF9" t="n">
         <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.6</v>
@@ -2812,25 +2812,25 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN9" t="n">
         <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP9" t="n">
         <v>24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
         <v>26</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
         <v>5.9</v>
@@ -2845,20 +2845,20 @@
         <v>8.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA9" t="n">
         <v>7.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I10" t="n">
         <v>2.92</v>
@@ -2904,7 +2904,7 @@
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.47</v>
@@ -2919,7 +2919,7 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
         <v>2.2</v>
@@ -2931,7 +2931,7 @@
         <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
         <v>1.94</v>
@@ -2940,7 +2940,7 @@
         <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2949,19 +2949,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB10" t="n">
         <v>9.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>38</v>
@@ -2988,7 +2988,7 @@
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>440</v>
       </c>
       <c r="AN10" t="n">
         <v>32</v>
@@ -3012,7 +3012,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
         <v>11.5</v>
@@ -3027,7 +3027,7 @@
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
         <v>42</v>
@@ -3042,10 +3042,10 @@
         <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BG10" t="n">
         <v>30</v>
@@ -3060,7 +3060,7 @@
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="H11" t="n">
         <v>6.2</v>
@@ -3170,7 +3170,7 @@
         <v>4.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
         <v>2.22</v>
@@ -3194,7 +3194,7 @@
         <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X11" t="n">
         <v>22</v>
@@ -3230,7 +3230,7 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="AJ11" t="n">
         <v>15</v>
@@ -3257,10 +3257,10 @@
         <v>20</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -3284,7 +3284,7 @@
         <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB11" t="n">
         <v>13</v>
@@ -3293,16 +3293,16 @@
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF11" t="n">
         <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="n">
         <v>3.85</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
         <v>2.12</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.3</v>
@@ -3439,19 +3439,19 @@
         <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
         <v>1.9</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y12" t="n">
         <v>13</v>
@@ -3514,7 +3514,7 @@
         <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
@@ -3538,7 +3538,7 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB12" t="n">
         <v>11.5</v>
@@ -3547,13 +3547,13 @@
         <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
         <v>12</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
@@ -3696,7 +3696,7 @@
         <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V13" t="n">
         <v>1.27</v>
@@ -3705,7 +3705,7 @@
         <v>1.92</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y13" t="n">
         <v>13</v>
@@ -3717,10 +3717,10 @@
         <v>120</v>
       </c>
       <c r="AB13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC13" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
         <v>19.5</v>
@@ -3738,13 +3738,13 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>210</v>
+        <v>380</v>
       </c>
       <c r="AJ13" t="n">
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
@@ -3768,7 +3768,7 @@
         <v>28</v>
       </c>
       <c r="AS13" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
@@ -3792,10 +3792,10 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
         <v>23</v>
@@ -3804,77 +3804,77 @@
         <v>44</v>
       </c>
       <c r="BE13" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ13" t="n">
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO13" t="n">
         <v>3.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA13" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G14" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H14" t="n">
         <v>3.4</v>
@@ -3917,7 +3917,7 @@
         <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
         <v>3.2</v>
@@ -3932,25 +3932,25 @@
         <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
         <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
         <v>1.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
         <v>1.37</v>
@@ -3971,7 +3971,7 @@
         <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC14" t="n">
         <v>7.4</v>
@@ -3980,7 +3980,7 @@
         <v>15.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="n">
         <v>15.5</v>
@@ -3992,16 +3992,16 @@
         <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AJ14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
@@ -4010,10 +4010,10 @@
         <v>30</v>
       </c>
       <c r="AO14" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
@@ -4022,7 +4022,7 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>7.6</v>
@@ -4034,7 +4034,7 @@
         <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
         <v>12.5</v>
@@ -4046,7 +4046,7 @@
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
         <v>11.5</v>
@@ -4058,19 +4058,19 @@
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="n">
         <v>3.05</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN14" t="n">
         <v>5.2</v>
@@ -4091,13 +4091,13 @@
         <v>4.2</v>
       </c>
       <c r="BP14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ14" t="n">
         <v>9</v>
       </c>
       <c r="BR14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS14" t="n">
         <v>11.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -4171,13 +4171,13 @@
         <v>2.14</v>
       </c>
       <c r="J15" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K15" t="n">
         <v>3.45</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
@@ -4198,7 +4198,7 @@
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T15" t="n">
         <v>2.16</v>
@@ -4207,7 +4207,7 @@
         <v>1.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W15" t="n">
         <v>1.23</v>
@@ -4267,10 +4267,10 @@
         <v>32</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="AR15" t="n">
         <v>3.6</v>
@@ -4279,7 +4279,7 @@
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU15" t="n">
         <v>6.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -4413,175 +4413,175 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
         <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P16" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S16" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="X16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="AB16" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI16" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
         <v>34</v>
       </c>
       <c r="AL16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AO16" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="AR16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS16" t="n">
         <v>5.1</v>
       </c>
-      <c r="AS16" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AT16" t="n">
-        <v>2.98</v>
+        <v>5.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>4.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BI16" t="n">
         <v>2.24</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK16" t="n">
         <v>6.6</v>
@@ -4590,53 +4590,53 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.24</v>
+        <v>13</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BP16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.96</v>
+        <v>7.4</v>
       </c>
       <c r="BR16" t="n">
         <v>44</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.18</v>
+        <v>11</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="BZ16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
         <v>3.55</v>
@@ -4685,13 +4685,13 @@
         <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
@@ -4703,7 +4703,7 @@
         <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
         <v>4.1</v>
@@ -4715,7 +4715,7 @@
         <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W17" t="n">
         <v>2.08</v>
@@ -4796,7 +4796,7 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -857,79 +857,79 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>40</v>
@@ -938,34 +938,34 @@
         <v>16</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
         <v>23</v>
       </c>
       <c r="AO2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
         <v>11</v>
@@ -977,7 +977,7 @@
         <v>42</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
         <v>6.6</v>
@@ -995,7 +995,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
         <v>34</v>
@@ -1007,22 +1007,22 @@
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
         <v>65</v>
       </c>
       <c r="BF2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
@@ -1034,43 +1034,43 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
         <v>5.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU2" t="n">
         <v>5.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -1111,184 +1111,184 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z3" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK3" t="n">
         <v>17.5</v>
       </c>
-      <c r="AK3" t="n">
-        <v>23</v>
-      </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT3" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>310</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>17.5</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BA3" t="n">
         <v>46</v>
       </c>
-      <c r="AX3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>42</v>
-      </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC3" t="n">
         <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="BF3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
         <v>44</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
         <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
@@ -1300,16 +1300,16 @@
         <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS3" t="n">
         <v>9</v>
       </c>
       <c r="BT3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU3" t="n">
         <v>5.6</v>
@@ -1321,20 +1321,20 @@
         <v>10.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
         <v>11</v>
       </c>
       <c r="BZ3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA3" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="H4" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="I4" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
         <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1395,13 +1395,13 @@
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
         <v>2.38</v>
@@ -1422,76 +1422,76 @@
         <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="n">
         <v>17</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ4" t="n">
         <v>36</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>28</v>
       </c>
       <c r="AM4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP4" t="n">
         <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>22</v>
@@ -1509,10 +1509,10 @@
         <v>26</v>
       </c>
       <c r="BB4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>25</v>
@@ -1521,16 +1521,16 @@
         <v>40</v>
       </c>
       <c r="BF4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.4</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN4" t="n">
         <v>6</v>
@@ -1569,7 +1569,7 @@
         <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW4" t="n">
         <v>14</v>
@@ -1584,11 +1584,11 @@
         <v>15</v>
       </c>
       <c r="CA4" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G5" t="n">
         <v>3.3</v>
       </c>
-      <c r="G5" t="n">
-        <v>3.4</v>
-      </c>
       <c r="H5" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.42</v>
@@ -1643,16 +1643,16 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R5" t="n">
         <v>1.37</v>
@@ -1661,22 +1661,22 @@
         <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
         <v>15.5</v>
@@ -1685,58 +1685,58 @@
         <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
         <v>26</v>
       </c>
       <c r="AF5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>40</v>
       </c>
       <c r="AJ5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
         <v>19.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1745,10 +1745,10 @@
         <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
         <v>20</v>
@@ -1760,10 +1760,10 @@
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC5" t="n">
         <v>32</v>
@@ -1772,13 +1772,13 @@
         <v>40</v>
       </c>
       <c r="BE5" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BF5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.4</v>
@@ -1790,59 +1790,59 @@
         <v>9.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR5" t="n">
         <v>38</v>
       </c>
       <c r="BS5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT5" t="n">
         <v>5.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>30</v>
       </c>
       <c r="BY5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>27</v>
       </c>
       <c r="CA5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
         <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
         <v>1.6</v>
@@ -1897,7 +1897,7 @@
         <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O6" t="n">
         <v>1.56</v>
@@ -1906,7 +1906,7 @@
         <v>1.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
@@ -1915,16 +1915,16 @@
         <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1942,7 +1942,7 @@
         <v>48</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1981,58 +1981,58 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY6" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
         <v>2.7</v>
@@ -2056,47 +2056,47 @@
         <v>4.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -2145,13 +2145,13 @@
         <v>3.15</v>
       </c>
       <c r="L7" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="M7" t="n">
         <v>1.18</v>
       </c>
       <c r="N7" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="O7" t="n">
         <v>1.75</v>
@@ -2160,7 +2160,7 @@
         <v>1.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.1</v>
@@ -2169,16 +2169,16 @@
         <v>7.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
         <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X7" t="n">
         <v>6.6</v>
@@ -2235,10 +2235,10 @@
         <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR7" t="n">
         <v>4.9</v>
@@ -2247,10 +2247,10 @@
         <v>6</v>
       </c>
       <c r="AT7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU7" t="n">
         <v>3.65</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.55</v>
       </c>
       <c r="AV7" t="n">
         <v>4.8</v>
@@ -2310,7 +2310,7 @@
         <v>6.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
         <v>40</v>
@@ -2328,7 +2328,7 @@
         <v>6.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BV7" t="n">
         <v>38</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -2381,40 +2381,40 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
         <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
         <v>1.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
@@ -2423,16 +2423,16 @@
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
         <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="X8" t="n">
         <v>8.6</v>
@@ -2447,19 +2447,19 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
@@ -2471,13 +2471,13 @@
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
@@ -2489,58 +2489,58 @@
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="n">
         <v>2.76</v>
@@ -2552,25 +2552,25 @@
         <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BN8" t="n">
         <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU8" t="n">
         <v>4.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G9" t="n">
         <v>3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
@@ -2659,31 +2659,31 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
       </c>
       <c r="P9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U9" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.15</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W9" t="n">
         <v>1.37</v>
@@ -2695,7 +2695,7 @@
         <v>22</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA9" t="n">
         <v>30</v>
@@ -2704,7 +2704,7 @@
         <v>32</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
         <v>12.5</v>
@@ -2713,13 +2713,13 @@
         <v>18.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>27</v>
@@ -2731,34 +2731,34 @@
         <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
         <v>48</v>
       </c>
       <c r="AN9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AP9" t="n">
         <v>30</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV9" t="n">
         <v>9.800000000000001</v>
@@ -2773,34 +2773,34 @@
         <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB9" t="n">
         <v>48</v>
       </c>
       <c r="BC9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG9" t="n">
         <v>6.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.6</v>
@@ -2812,31 +2812,31 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
         <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
         <v>24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
         <v>26</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT9" t="n">
         <v>5.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
         <v>13</v>
@@ -2848,17 +2848,17 @@
         <v>18.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G10" t="n">
         <v>2.58</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.64</v>
-      </c>
       <c r="H10" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
         <v>3.8</v>
@@ -2919,58 +2919,58 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
         <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
         <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
@@ -2979,22 +2979,22 @@
         <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK10" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
@@ -3003,16 +3003,16 @@
         <v>9.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
         <v>11.5</v>
@@ -3021,88 +3021,88 @@
         <v>30</v>
       </c>
       <c r="AX10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD10" t="n">
         <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>16.5</v>
+        <v>90</v>
       </c>
       <c r="BF10" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="BG10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.35</v>
@@ -3170,22 +3170,22 @@
         <v>4.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
         <v>2.96</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
         <v>2.06</v>
@@ -3194,22 +3194,22 @@
         <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z11" t="n">
         <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
         <v>10.5</v>
@@ -3218,10 +3218,10 @@
         <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG11" t="n">
         <v>9.6</v>
@@ -3236,137 +3236,137 @@
         <v>15</v>
       </c>
       <c r="AK11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AP11" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BH11" t="n">
         <v>3.85</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR11" t="n">
         <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BV11" t="n">
         <v>55</v>
       </c>
       <c r="BW11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
         <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -3439,7 +3439,7 @@
         <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
         <v>1.9</v>
@@ -3451,7 +3451,7 @@
         <v>1.9</v>
       </c>
       <c r="X12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
         <v>13</v>
@@ -3469,13 +3469,13 @@
         <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AE12" t="n">
         <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
@@ -3490,7 +3490,7 @@
         <v>110</v>
       </c>
       <c r="AK12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3499,10 +3499,10 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
         <v>9.6</v>
@@ -3511,10 +3511,10 @@
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
@@ -3526,34 +3526,34 @@
         <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="BG12" t="n">
         <v>12</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN12" t="n">
         <v>4.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
         <v>1.53</v>
@@ -3675,22 +3675,22 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T13" t="n">
         <v>2.08</v>
@@ -3699,10 +3699,10 @@
         <v>1.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
         <v>9.6</v>
@@ -3714,7 +3714,7 @@
         <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>310</v>
       </c>
       <c r="AB13" t="n">
         <v>7.2</v>
@@ -3723,7 +3723,7 @@
         <v>7.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
         <v>80</v>
@@ -3741,7 +3741,7 @@
         <v>380</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>65</v>
@@ -3753,10 +3753,10 @@
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
@@ -3765,10 +3765,10 @@
         <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
@@ -3780,10 +3780,10 @@
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY13" t="n">
         <v>9.800000000000001</v>
@@ -3792,10 +3792,10 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
         <v>23</v>
@@ -3804,77 +3804,77 @@
         <v>44</v>
       </c>
       <c r="BE13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BF13" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>16.5</v>
+        <v>70</v>
       </c>
       <c r="BH13" t="n">
         <v>2.98</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BJ13" t="n">
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO13" t="n">
         <v>3.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G14" t="n">
         <v>2.54</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>3.05</v>
@@ -3923,31 +3923,31 @@
         <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U14" t="n">
         <v>1.96</v>
@@ -3959,7 +3959,7 @@
         <v>1.65</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
         <v>11.5</v>
@@ -3968,7 +3968,7 @@
         <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB14" t="n">
         <v>8.6</v>
@@ -3980,10 +3980,10 @@
         <v>15.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG14" t="n">
         <v>11.5</v>
@@ -3992,7 +3992,7 @@
         <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
         <v>38</v>
@@ -4001,13 +4001,13 @@
         <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
         <v>60</v>
@@ -4022,10 +4022,10 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
@@ -4034,7 +4034,7 @@
         <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AX14" t="n">
         <v>12.5</v>
@@ -4046,28 +4046,28 @@
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="BB14" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BC14" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BD14" t="n">
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI14" t="n">
         <v>2.56</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN14" t="n">
         <v>5.2</v>
@@ -4094,13 +4094,13 @@
         <v>20</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR14" t="n">
         <v>38</v>
       </c>
       <c r="BS14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT14" t="n">
         <v>6.4</v>
@@ -4112,13 +4112,13 @@
         <v>29</v>
       </c>
       <c r="BW14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -4159,40 +4159,40 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
@@ -4210,7 +4210,7 @@
         <v>1.89</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X15" t="n">
         <v>9</v>
@@ -4324,7 +4324,7 @@
         <v>2.78</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BJ15" t="n">
         <v>12.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -4413,46 +4413,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H16" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I16" t="n">
         <v>5.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
         <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.17</v>
       </c>
       <c r="S16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
         <v>2.3</v>
@@ -4464,19 +4464,19 @@
         <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA16" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB16" t="n">
         <v>7.2</v>
@@ -4485,7 +4485,7 @@
         <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>140</v>
@@ -4494,7 +4494,7 @@
         <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
         <v>36</v>
@@ -4527,10 +4527,10 @@
         <v>9.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT16" t="n">
         <v>5.4</v>
@@ -4560,10 +4560,10 @@
         <v>18.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
         <v>5.1</v>
@@ -4575,34 +4575,34 @@
         <v>5.1</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="BJ16" t="n">
         <v>13</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN16" t="n">
         <v>4.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR16" t="n">
         <v>44</v>
@@ -4611,7 +4611,7 @@
         <v>10.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU16" t="n">
         <v>5.3</v>
@@ -4620,7 +4620,7 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4632,11 +4632,11 @@
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -4667,31 +4667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
@@ -4709,16 +4709,16 @@
         <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
         <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
@@ -4736,7 +4736,7 @@
         <v>7.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
         <v>20</v>
@@ -4784,7 +4784,7 @@
         <v>7.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4796,7 +4796,7 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4808,7 +4808,7 @@
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB17" t="n">
         <v>17.5</v>
@@ -4820,31 +4820,31 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF17" t="n">
         <v>12.5</v>
       </c>
       <c r="BG17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK17" t="n">
         <v>8.6</v>
       </c>
-      <c r="BH17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN17" t="n">
         <v>4.5</v>
@@ -4853,16 +4853,16 @@
         <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR17" t="n">
         <v>32</v>
       </c>
       <c r="BS17" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT17" t="n">
         <v>8</v>
@@ -4871,26 +4871,26 @@
         <v>6.4</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
         <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -860,19 +860,19 @@
         <v>2.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -881,127 +881,127 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.98</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
         <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
         <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -1010,22 +1010,22 @@
         <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF2" t="n">
         <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2" t="n">
         <v>7.6</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>5.4</v>
@@ -1046,13 +1046,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.6</v>
@@ -1064,13 +1064,13 @@
         <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1138,82 +1138,82 @@
         <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="n">
         <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL3" t="n">
         <v>32</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AO3" t="n">
         <v>70</v>
@@ -1222,25 +1222,25 @@
         <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
         <v>36</v>
       </c>
       <c r="AS3" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX3" t="n">
         <v>9.800000000000001</v>
@@ -1249,49 +1249,49 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
         <v>27</v>
       </c>
       <c r="BE3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO3" t="n">
         <v>3.85</v>
@@ -1306,7 +1306,7 @@
         <v>24</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>9.199999999999999</v>
@@ -1315,26 +1315,26 @@
         <v>5.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW3" t="n">
         <v>10.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY3" t="n">
         <v>11</v>
       </c>
       <c r="BZ3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G4" t="n">
         <v>2.56</v>
       </c>
       <c r="H4" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1383,34 +1383,34 @@
         <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T4" t="n">
         <v>1.51</v>
       </c>
       <c r="U4" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V4" t="n">
         <v>1.53</v>
@@ -1419,7 +1419,7 @@
         <v>1.64</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
         <v>19</v>
@@ -1431,13 +1431,13 @@
         <v>44</v>
       </c>
       <c r="AB4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>26</v>
@@ -1446,40 +1446,40 @@
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>13.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ4" t="n">
         <v>36</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN4" t="n">
         <v>12.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ4" t="n">
         <v>17</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS4" t="n">
         <v>38</v>
@@ -1488,28 +1488,28 @@
         <v>15.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>26</v>
       </c>
       <c r="BB4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1527,10 +1527,10 @@
         <v>14</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.4</v>
@@ -1539,7 +1539,7 @@
         <v>7.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM4" t="n">
         <v>13</v>
@@ -1566,7 +1566,7 @@
         <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
         <v>18.5</v>
@@ -1581,14 +1581,14 @@
         <v>18</v>
       </c>
       <c r="BZ4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
@@ -1637,109 +1637,109 @@
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
         <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF5" t="n">
         <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
         <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7.4</v>
@@ -1751,52 +1751,52 @@
         <v>23</v>
       </c>
       <c r="AX5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM5" t="n">
         <v>15.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>17</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
@@ -1805,22 +1805,22 @@
         <v>5.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BQ5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BR5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
         <v>17.5</v>
@@ -1829,20 +1829,20 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BZ5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="CA5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
         <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
@@ -1915,22 +1915,22 @@
         <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1978,22 +1978,22 @@
         <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS6" t="n">
         <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU6" t="n">
         <v>5.6</v>
@@ -2011,40 +2011,40 @@
         <v>5.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2.88</v>
       </c>
-      <c r="G7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.42</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.37</v>
-      </c>
       <c r="X7" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AM7" t="n">
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK7" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.85</v>
+        <v>7.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.82</v>
+        <v>7</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU7" t="n">
         <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.82</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="X8" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
       </c>
       <c r="AF8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG8" t="n">
         <v>12</v>
       </c>
-      <c r="AG8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS8" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AT8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX8" t="n">
         <v>10</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB8" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>21</v>
       </c>
       <c r="BC8" t="n">
         <v>22</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BN8" t="n">
         <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BP8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -2635,70 +2635,70 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P9" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="T9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="U9" t="n">
         <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
         <v>48</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="n">
         <v>22</v>
       </c>
       <c r="AA9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AB9" t="n">
         <v>32</v>
@@ -2710,49 +2710,49 @@
         <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
         <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AN9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR9" t="n">
         <v>18</v>
       </c>
-      <c r="AO9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AS9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT9" t="n">
         <v>25</v>
@@ -2761,46 +2761,46 @@
         <v>10.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AY9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BB9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH9" t="n">
         <v>5.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.6</v>
@@ -2812,25 +2812,25 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR9" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9" t="n">
         <v>5.9</v>
@@ -2839,26 +2839,26 @@
         <v>5</v>
       </c>
       <c r="BV9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
         <v>8.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA9" t="n">
         <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
         <v>3.8</v>
@@ -2913,28 +2913,28 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q10" t="n">
         <v>2.16</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
         <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.5</v>
@@ -2946,10 +2946,10 @@
         <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
         <v>55</v>
@@ -2961,10 +2961,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
         <v>15.5</v>
@@ -3000,7 +3000,7 @@
         <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>17</v>
@@ -3051,58 +3051,58 @@
         <v>32</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L11" t="n">
         <v>1.35</v>
@@ -3179,22 +3179,22 @@
         <v>1.79</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
         <v>2.96</v>
       </c>
       <c r="T11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X11" t="n">
         <v>19</v>
@@ -3206,7 +3206,7 @@
         <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AB11" t="n">
         <v>9.6</v>
@@ -3230,10 +3230,10 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>390</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK11" t="n">
         <v>16</v>
@@ -3248,10 +3248,10 @@
         <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>22</v>
@@ -3266,7 +3266,7 @@
         <v>8.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV11" t="n">
         <v>21</v>
@@ -3284,10 +3284,10 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
@@ -3296,13 +3296,13 @@
         <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BH11" t="n">
         <v>3.85</v>
@@ -3314,7 +3314,7 @@
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3344,7 +3344,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BV11" t="n">
         <v>55</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
         <v>2.1</v>
@@ -3412,7 +3412,7 @@
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -3430,10 +3430,10 @@
         <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
         <v>4.7</v>
@@ -3445,34 +3445,34 @@
         <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
         <v>1.9</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB12" t="n">
         <v>7.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AF12" t="n">
         <v>11.5</v>
@@ -3481,82 +3481,82 @@
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AJ12" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="AK12" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>600</v>
+        <v>260</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS12" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
         <v>28</v>
       </c>
       <c r="BB12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BE12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BF12" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BH12" t="n">
         <v>2.96</v>
@@ -3568,13 +3568,13 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN12" t="n">
         <v>4.6</v>
@@ -3589,7 +3589,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS12" t="n">
         <v>11.5</v>
@@ -3598,7 +3598,7 @@
         <v>7.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3607,7 +3607,7 @@
         <v>12</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
         <v>13</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.53</v>
@@ -3681,7 +3681,7 @@
         <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
         <v>2.46</v>
@@ -3693,19 +3693,19 @@
         <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="X13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
         <v>13</v>
@@ -3723,13 +3723,13 @@
         <v>7.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE13" t="n">
         <v>80</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
@@ -3738,10 +3738,10 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>380</v>
+        <v>210</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
         <v>65</v>
@@ -3750,13 +3750,13 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AN13" t="n">
         <v>22</v>
       </c>
       <c r="AO13" t="n">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
@@ -3765,10 +3765,10 @@
         <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS13" t="n">
-        <v>16.5</v>
+        <v>85</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
@@ -3780,7 +3780,7 @@
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX13" t="n">
         <v>9.6</v>
@@ -3789,13 +3789,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
         <v>23</v>
@@ -3804,31 +3804,31 @@
         <v>44</v>
       </c>
       <c r="BE13" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="BF13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH13" t="n">
         <v>2.98</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ13" t="n">
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN13" t="n">
         <v>4.6</v>
@@ -3840,16 +3840,16 @@
         <v>16</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU13" t="n">
         <v>4.9</v>
@@ -3858,23 +3858,23 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>2.54</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
         <v>3.7</v>
@@ -3947,7 +3947,7 @@
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
         <v>1.96</v>
@@ -3956,7 +3956,7 @@
         <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
         <v>10.5</v>
@@ -4022,10 +4022,10 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
@@ -4034,7 +4034,7 @@
         <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AX14" t="n">
         <v>12.5</v>
@@ -4049,7 +4049,7 @@
         <v>44</v>
       </c>
       <c r="BB14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC14" t="n">
         <v>23</v>
@@ -4061,10 +4061,10 @@
         <v>29</v>
       </c>
       <c r="BF14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BG14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH14" t="n">
         <v>2.98</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BN14" t="n">
         <v>5.2</v>
@@ -4094,13 +4094,13 @@
         <v>20</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BR14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT14" t="n">
         <v>6.4</v>
@@ -4112,13 +4112,13 @@
         <v>29</v>
       </c>
       <c r="BW14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4165,13 @@
         <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I15" t="n">
         <v>2.12</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
         <v>3.4</v>
@@ -4183,7 +4183,7 @@
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O15" t="n">
         <v>1.54</v>
@@ -4201,37 +4201,37 @@
         <v>5.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
         <v>9</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA15" t="n">
         <v>32</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC15" t="n">
         <v>9</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE15" t="n">
         <v>36</v>
@@ -4240,10 +4240,10 @@
         <v>42</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH15" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
         <v>75</v>
@@ -4264,7 +4264,7 @@
         <v>180</v>
       </c>
       <c r="AO15" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP15" t="n">
         <v>7.2</v>
@@ -4273,52 +4273,52 @@
         <v>5.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AU15" t="n">
         <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH15" t="n">
         <v>2.78</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -4413,25 +4413,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H16" t="n">
         <v>5.3</v>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
         <v>1.13</v>
@@ -4440,10 +4440,10 @@
         <v>2.58</v>
       </c>
       <c r="O16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q16" t="n">
         <v>2.8</v>
@@ -4464,10 +4464,10 @@
         <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y16" t="n">
         <v>15</v>
@@ -4476,31 +4476,31 @@
         <v>48</v>
       </c>
       <c r="AA16" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF16" t="n">
         <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
         <v>36</v>
       </c>
       <c r="AI16" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AJ16" t="n">
         <v>26</v>
@@ -4518,22 +4518,22 @@
         <v>27</v>
       </c>
       <c r="AO16" t="n">
-        <v>310</v>
+        <v>390</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
@@ -4542,37 +4542,37 @@
         <v>20</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
         <v>8.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="BA16" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.8</v>
+        <v>23</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="n">
         <v>2.66</v>
@@ -4590,16 +4590,16 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN16" t="n">
         <v>4.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ16" t="n">
         <v>7.8</v>
@@ -4608,25 +4608,25 @@
         <v>44</v>
       </c>
       <c r="BS16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT16" t="n">
         <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H17" t="n">
         <v>4.7</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
@@ -4697,22 +4697,22 @@
         <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
         <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
         <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V17" t="n">
         <v>1.25</v>
@@ -4724,22 +4724,22 @@
         <v>13</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
         <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC17" t="n">
         <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE17" t="n">
         <v>90</v>
@@ -4751,13 +4751,13 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>25</v>
       </c>
       <c r="AK17" t="n">
         <v>22</v>
@@ -4772,7 +4772,7 @@
         <v>18.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -4781,10 +4781,10 @@
         <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.8</v>
+        <v>27</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4796,7 +4796,7 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4808,7 +4808,7 @@
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="BB17" t="n">
         <v>17.5</v>
@@ -4820,22 +4820,22 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK17" t="n">
         <v>8.6</v>
@@ -4871,7 +4871,7 @@
         <v>6.4</v>
       </c>
       <c r="BV17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
         <v>12.5</v>
@@ -4883,14 +4883,14 @@
         <v>13.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="CA17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -857,64 +857,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
         <v>3.25</v>
       </c>
       <c r="I2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.45</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y2" t="n">
         <v>15.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>14</v>
       </c>
       <c r="Z2" t="n">
         <v>24</v>
@@ -929,7 +929,7 @@
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
         <v>36</v>
@@ -938,19 +938,19 @@
         <v>16.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
         <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
         <v>38</v>
@@ -959,7 +959,7 @@
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="n">
         <v>38</v>
@@ -968,73 +968,73 @@
         <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
         <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>29</v>
       </c>
       <c r="AX2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>14</v>
       </c>
-      <c r="AY2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA2" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BF2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
         <v>5.4</v>
@@ -1043,16 +1043,16 @@
         <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT2" t="n">
         <v>6.6</v>
@@ -1064,13 +1064,13 @@
         <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>38</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -1111,199 +1111,199 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
         <v>17</v>
       </c>
       <c r="AK3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM3" t="n">
-        <v>390</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3" t="n">
         <v>17</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17.5</v>
       </c>
       <c r="AW3" t="n">
         <v>50</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BR3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BS3" t="n">
         <v>8.800000000000001</v>
@@ -1312,29 +1312,29 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX3" t="n">
         <v>44</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>48</v>
       </c>
       <c r="BY3" t="n">
         <v>11</v>
       </c>
       <c r="BZ3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CA3" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -1377,73 +1377,73 @@
         <v>2.86</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="S4" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="U4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
         <v>1.64</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1452,31 +1452,31 @@
         <v>13.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>36</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>27</v>
       </c>
       <c r="AM4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>22</v>
@@ -1485,10 +1485,10 @@
         <v>38</v>
       </c>
       <c r="AT4" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
@@ -1506,61 +1506,61 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK4" t="n">
         <v>7.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ4" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS4" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
@@ -1569,26 +1569,26 @@
         <v>5.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BX4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BZ4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
         <v>2.46</v>
@@ -1631,19 +1631,19 @@
         <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.29</v>
@@ -1652,22 +1652,22 @@
         <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
         <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
         <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
         <v>1.46</v>
@@ -1676,7 +1676,7 @@
         <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
         <v>16</v>
@@ -1691,7 +1691,7 @@
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
         <v>25</v>
@@ -1700,13 +1700,13 @@
         <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ5" t="n">
         <v>55</v>
@@ -1727,10 +1727,10 @@
         <v>18.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
         <v>14.5</v>
@@ -1751,7 +1751,7 @@
         <v>23</v>
       </c>
       <c r="AX5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
@@ -1763,7 +1763,7 @@
         <v>32</v>
       </c>
       <c r="BB5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1772,19 +1772,19 @@
         <v>38</v>
       </c>
       <c r="BE5" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="BF5" t="n">
         <v>26</v>
       </c>
       <c r="BG5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
@@ -1796,7 +1796,7 @@
         <v>110</v>
       </c>
       <c r="BM5" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
@@ -1808,16 +1808,16 @@
         <v>24</v>
       </c>
       <c r="BQ5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BR5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU5" t="n">
         <v>4.9</v>
@@ -1826,23 +1826,23 @@
         <v>17.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BZ5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA5" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -1882,13 +1882,13 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.58</v>
@@ -1900,37 +1900,37 @@
         <v>2.48</v>
       </c>
       <c r="O6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
         <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
         <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1942,7 +1942,7 @@
         <v>48</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1954,7 +1954,7 @@
         <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
         <v>500</v>
@@ -1981,7 +1981,7 @@
         <v>140</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.5</v>
@@ -1993,7 +1993,7 @@
         <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AU6" t="n">
         <v>5.6</v>
@@ -2011,7 +2011,7 @@
         <v>5.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
@@ -2020,19 +2020,19 @@
         <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="BH6" t="n">
         <v>2.74</v>
@@ -2044,7 +2044,7 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.97</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.71</v>
+        <v>4.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.77</v>
+        <v>4.2</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.73</v>
+        <v>4.3</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="H7" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
         <v>2.78</v>
@@ -2145,7 +2145,7 @@
         <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
         <v>1.13</v>
@@ -2157,7 +2157,7 @@
         <v>1.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Q7" t="n">
         <v>2.88</v>
@@ -2166,34 +2166,34 @@
         <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
         <v>8.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
@@ -2205,22 +2205,22 @@
         <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
         <v>260</v>
@@ -2229,109 +2229,109 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO7" t="n">
         <v>70</v>
       </c>
-      <c r="AO7" t="n">
-        <v>65</v>
-      </c>
       <c r="AP7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BB7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF7" t="n">
         <v>7</v>
       </c>
-      <c r="AU7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
         <v>2.78</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ7" t="n">
         <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS7" t="n">
         <v>7</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW7" t="n">
         <v>6.2</v>
@@ -2340,17 +2340,17 @@
         <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CA7" t="n">
         <v>7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -2381,61 +2381,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
         <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U8" t="n">
         <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
         <v>13.5</v>
@@ -2447,25 +2447,25 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
@@ -2477,7 +2477,7 @@
         <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
@@ -2486,19 +2486,19 @@
         <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AP8" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
         <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
         <v>5.6</v>
@@ -2510,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -2522,16 +2522,16 @@
         <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BC8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD8" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BE8" t="n">
         <v>28</v>
@@ -2540,43 +2540,43 @@
         <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
         <v>3.85</v>
       </c>
       <c r="BP8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT8" t="n">
         <v>8.199999999999999</v>
@@ -2588,13 +2588,13 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -2635,130 +2635,130 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.04</v>
-      </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
         <v>48</v>
       </c>
       <c r="Y9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
         <v>28</v>
       </c>
       <c r="AB9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD9" t="n">
         <v>12.5</v>
       </c>
       <c r="AE9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG9" t="n">
         <v>17.5</v>
       </c>
-      <c r="AF9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>17</v>
-      </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK9" t="n">
         <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AP9" t="n">
         <v>40</v>
       </c>
-      <c r="AN9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>34</v>
-      </c>
       <c r="AQ9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR9" t="n">
         <v>19</v>
       </c>
-      <c r="AR9" t="n">
-        <v>18</v>
-      </c>
       <c r="AS9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AU9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>11</v>
@@ -2767,22 +2767,22 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AY9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
         <v>18</v>
       </c>
       <c r="BB9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BD9" t="n">
         <v>25</v>
@@ -2794,25 +2794,25 @@
         <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BJ9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK9" t="n">
         <v>5.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BN9" t="n">
         <v>8</v>
@@ -2827,7 +2827,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS9" t="n">
         <v>8.199999999999999</v>
@@ -2836,7 +2836,7 @@
         <v>5.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>12.5</v>
@@ -2845,20 +2845,20 @@
         <v>8.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BY9" t="n">
         <v>7.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I10" t="n">
         <v>3.05</v>
@@ -2904,67 +2904,67 @@
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
         <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="n">
         <v>15.5</v>
@@ -2973,31 +2973,31 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL10" t="n">
         <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
       </c>
       <c r="AN10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO10" t="n">
         <v>36</v>
       </c>
-      <c r="AO10" t="n">
-        <v>44</v>
-      </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>10</v>
@@ -3006,16 +3006,16 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW10" t="n">
         <v>30</v>
@@ -3024,70 +3024,70 @@
         <v>14</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BB10" t="n">
         <v>32</v>
       </c>
       <c r="BC10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BG10" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU10" t="n">
         <v>4.9</v>
@@ -3096,13 +3096,13 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G11" t="n">
         <v>1.57</v>
@@ -3155,10 +3155,10 @@
         <v>7.2</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.35</v>
@@ -3167,34 +3167,34 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
         <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X11" t="n">
         <v>19</v>
@@ -3203,22 +3203,22 @@
         <v>26</v>
       </c>
       <c r="Z11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA11" t="n">
         <v>700</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
         <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="AF11" t="n">
         <v>9.800000000000001</v>
@@ -3230,7 +3230,7 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
         <v>14.5</v>
@@ -3242,10 +3242,10 @@
         <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO11" t="n">
         <v>100</v>
@@ -3284,31 +3284,31 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD11" t="n">
         <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
         <v>55</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="BN11" t="n">
         <v>4.2</v>
@@ -3332,13 +3332,13 @@
         <v>10</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR11" t="n">
         <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT11" t="n">
         <v>9.800000000000001</v>
@@ -3350,23 +3350,23 @@
         <v>55</v>
       </c>
       <c r="BW11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
         <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
         <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
         <v>3.5</v>
@@ -3427,13 +3427,13 @@
         <v>1.45</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
         <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
         <v>4.7</v>
@@ -3445,10 +3445,10 @@
         <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -3460,7 +3460,7 @@
         <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AB12" t="n">
         <v>7.4</v>
@@ -3484,19 +3484,19 @@
         <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>370</v>
+        <v>230</v>
       </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
         <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AM12" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>22</v>
@@ -3514,7 +3514,7 @@
         <v>27</v>
       </c>
       <c r="AS12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT12" t="n">
         <v>6.6</v>
@@ -3550,13 +3550,13 @@
         <v>42</v>
       </c>
       <c r="BE12" t="n">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="BF12" t="n">
         <v>19.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH12" t="n">
         <v>2.96</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>15.5</v>
+        <v>140</v>
       </c>
       <c r="BN12" t="n">
         <v>4.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -3651,61 +3651,61 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
         <v>2.02</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.08</v>
-      </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
         <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
         <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
         <v>1.84</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
         <v>13</v>
@@ -3714,7 +3714,7 @@
         <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>310</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
         <v>7.2</v>
@@ -3738,22 +3738,22 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>110</v>
@@ -3765,10 +3765,10 @@
         <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS13" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
@@ -3777,19 +3777,19 @@
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW13" t="n">
         <v>48</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
         <v>75</v>
@@ -3798,22 +3798,22 @@
         <v>22</v>
       </c>
       <c r="BC13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
         <v>44</v>
       </c>
       <c r="BE13" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="BF13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BI13" t="n">
         <v>2.42</v>
@@ -3822,13 +3822,13 @@
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="BN13" t="n">
         <v>4.6</v>
@@ -3840,41 +3840,41 @@
         <v>16</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT13" t="n">
         <v>8</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -3911,16 +3911,16 @@
         <v>2.54</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I14" t="n">
         <v>3.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
         <v>1.5</v>
@@ -3935,7 +3935,7 @@
         <v>1.44</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
         <v>2.32</v>
@@ -3956,7 +3956,7 @@
         <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
         <v>10.5</v>
@@ -3980,7 +3980,7 @@
         <v>15.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF14" t="n">
         <v>16</v>
@@ -3992,7 +3992,7 @@
         <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="n">
         <v>38</v>
@@ -4001,7 +4001,7 @@
         <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
@@ -4025,7 +4025,7 @@
         <v>48</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
@@ -4046,19 +4046,19 @@
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC14" t="n">
         <v>23</v>
       </c>
       <c r="BD14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="BF14" t="n">
         <v>22</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="BN14" t="n">
         <v>5.2</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
         <v>1.58</v>
@@ -4186,7 +4186,7 @@
         <v>2.62</v>
       </c>
       <c r="O15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P15" t="n">
         <v>1.52</v>
@@ -4201,13 +4201,13 @@
         <v>5.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
         <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W15" t="n">
         <v>1.23</v>
@@ -4243,7 +4243,7 @@
         <v>23</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AI15" t="n">
         <v>75</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
         <v>5.3</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L16" t="n">
         <v>1.6</v>
@@ -4437,7 +4437,7 @@
         <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.57</v>
@@ -4446,13 +4446,13 @@
         <v>1.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
         <v>1.17</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="T16" t="n">
         <v>2.3</v>
@@ -4464,7 +4464,7 @@
         <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4476,13 +4476,13 @@
         <v>48</v>
       </c>
       <c r="AA16" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB16" t="n">
         <v>6.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
         <v>24</v>
@@ -4491,7 +4491,7 @@
         <v>150</v>
       </c>
       <c r="AF16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>12</v>
@@ -4509,7 +4509,7 @@
         <v>34</v>
       </c>
       <c r="AL16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
         <v>310</v>
@@ -4518,7 +4518,7 @@
         <v>27</v>
       </c>
       <c r="AO16" t="n">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="AP16" t="n">
         <v>7.2</v>
@@ -4530,7 +4530,7 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT16" t="n">
         <v>5.2</v>
@@ -4542,7 +4542,7 @@
         <v>20</v>
       </c>
       <c r="AW16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>8.6</v>
@@ -4554,7 +4554,7 @@
         <v>23</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB16" t="n">
         <v>20</v>
@@ -4566,7 +4566,7 @@
         <v>38</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF16" t="n">
         <v>21</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.9</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.94</v>
-      </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
         <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
         <v>1.5</v>
@@ -4712,34 +4712,34 @@
         <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA17" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
         <v>8.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>90</v>
@@ -4751,16 +4751,16 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>21</v>
       </c>
-      <c r="AI17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>22</v>
-      </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
         <v>48</v>
@@ -4769,7 +4769,7 @@
         <v>160</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
         <v>100</v>
@@ -4784,7 +4784,7 @@
         <v>27</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4796,7 +4796,7 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4820,10 +4820,10 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG17" t="n">
         <v>55</v>
@@ -4832,7 +4832,7 @@
         <v>3.15</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
@@ -4844,7 +4844,7 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BN17" t="n">
         <v>4.5</v>
@@ -4853,44 +4853,44 @@
         <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BR17" t="n">
         <v>32</v>
       </c>
       <c r="BS17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BU17" t="n">
         <v>6.4</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY17" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>13.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>28</v>
       </c>
       <c r="CA17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>4.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>11.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.66</v>
+        <v>3.05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>5.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="AC2" t="n">
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>36</v>
       </c>
-      <c r="AF2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI2" t="n">
+      <c r="BA2" t="n">
+        <v>160</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC2" t="n">
         <v>44</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM2" t="n">
+      <c r="BD2" t="n">
         <v>110</v>
       </c>
-      <c r="AN2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>30</v>
-      </c>
       <c r="BE2" t="n">
-        <v>48</v>
+        <v>380</v>
       </c>
       <c r="BF2" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BG2" t="n">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.5</v>
+        <v>1.27</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.6</v>
+        <v>950</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S3" t="n">
         <v>5.4</v>
       </c>
-      <c r="J3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.64</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="X3" t="n">
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD3" t="n">
         <v>25</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AE3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD3" t="n">
         <v>55</v>
       </c>
-      <c r="AA3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="BE3" t="n">
+        <v>210</v>
+      </c>
+      <c r="BF3" t="n">
         <v>17</v>
       </c>
-      <c r="AK3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="BG3" t="n">
+        <v>130</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>21</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BK3" t="n">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="BR3" t="n">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.5</v>
+        <v>75</v>
       </c>
       <c r="BX3" t="n">
-        <v>44</v>
+        <v>250</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="BZ3" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.4</v>
+        <v>90</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
         <v>2.56</v>
       </c>
       <c r="H4" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="I4" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
         <v>1.64</v>
       </c>
       <c r="X4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y4" t="n">
         <v>21</v>
@@ -1431,64 +1431,64 @@
         <v>42</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC4" t="n">
         <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AI4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP4" t="n">
         <v>28</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="AQ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR4" t="n">
         <v>23</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>22</v>
       </c>
       <c r="AS4" t="n">
         <v>38</v>
       </c>
       <c r="AT4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
@@ -1497,16 +1497,16 @@
         <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1515,25 +1515,25 @@
         <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BK4" t="n">
         <v>7.4</v>
@@ -1542,53 +1542,53 @@
         <v>60</v>
       </c>
       <c r="BM4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN4" t="n">
         <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BX4" t="n">
         <v>23</v>
       </c>
       <c r="BY4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BZ4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I5" t="n">
         <v>2.46</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
@@ -1643,58 +1643,58 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
         <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
         <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF5" t="n">
         <v>23</v>
@@ -1703,7 +1703,7 @@
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
         <v>36</v>
@@ -1712,19 +1712,19 @@
         <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
         <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
         <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP5" t="n">
         <v>15</v>
@@ -1739,16 +1739,16 @@
         <v>28</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
         <v>20</v>
@@ -1757,10 +1757,10 @@
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB5" t="n">
         <v>46</v>
@@ -1769,22 +1769,22 @@
         <v>30</v>
       </c>
       <c r="BD5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
         <v>65</v>
       </c>
       <c r="BF5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
@@ -1796,31 +1796,31 @@
         <v>110</v>
       </c>
       <c r="BM5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP5" t="n">
         <v>24</v>
       </c>
       <c r="BQ5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BR5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
         <v>17.5</v>
@@ -1829,20 +1829,20 @@
         <v>15.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>24</v>
+      </c>
+      <c r="CA5" t="n">
         <v>21</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>17.5</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
         <v>1.13</v>
@@ -1903,10 +1903,10 @@
         <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1915,16 +1915,16 @@
         <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1981,25 +1981,25 @@
         <v>140</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
         <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU6" t="n">
         <v>5.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
         <v>4.9</v>
@@ -2008,43 +2008,43 @@
         <v>5.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>3.95</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.3</v>
+        <v>1.95</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.5</v>
+        <v>1.93</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.92</v>
+        <v>2.42</v>
       </c>
       <c r="G7" t="n">
-        <v>3.55</v>
+        <v>2.52</v>
       </c>
       <c r="H7" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.65</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.13</v>
       </c>
-      <c r="N7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="U7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.66</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X7" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="AJ7" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AM7" t="n">
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AO7" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>13</v>
       </c>
-      <c r="AS7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BK7" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BS7" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="CA7" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
@@ -2408,40 +2408,40 @@
         <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
         <v>5.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V8" t="n">
         <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2450,10 +2450,10 @@
         <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>330</v>
@@ -2471,10 +2471,10 @@
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
         <v>100</v>
@@ -2483,46 +2483,46 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
         <v>23</v>
@@ -2531,55 +2531,55 @@
         <v>23</v>
       </c>
       <c r="BD8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="BJ8" t="n">
         <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU8" t="n">
         <v>6</v>
@@ -2588,13 +2588,13 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="G9" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="H9" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="J9" t="n">
         <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.2</v>
@@ -2659,46 +2659,46 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
         <v>48</v>
       </c>
       <c r="Y9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB9" t="n">
         <v>34</v>
@@ -2707,7 +2707,7 @@
         <v>13</v>
       </c>
       <c r="AD9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>16.5</v>
@@ -2716,10 +2716,10 @@
         <v>42</v>
       </c>
       <c r="AG9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI9" t="n">
         <v>21</v>
@@ -2728,37 +2728,37 @@
         <v>70</v>
       </c>
       <c r="AK9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>5.9</v>
       </c>
       <c r="AP9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AS9" t="n">
         <v>24</v>
       </c>
       <c r="AT9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV9" t="n">
         <v>11</v>
@@ -2770,13 +2770,13 @@
         <v>36</v>
       </c>
       <c r="AY9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ9" t="n">
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB9" t="n">
         <v>55</v>
@@ -2785,67 +2785,67 @@
         <v>29</v>
       </c>
       <c r="BD9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BM9" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BP9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU9" t="n">
         <v>5.1</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BY9" t="n">
         <v>7.4</v>
@@ -2854,11 +2854,11 @@
         <v>9.6</v>
       </c>
       <c r="CA9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H10" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
@@ -2907,49 +2907,49 @@
         <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
         <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
         <v>55</v>
@@ -2958,7 +2958,7 @@
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
         <v>13.5</v>
@@ -2967,19 +2967,19 @@
         <v>38</v>
       </c>
       <c r="AF10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2988,10 +2988,10 @@
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>36</v>
@@ -3000,19 +3000,19 @@
         <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
@@ -3024,16 +3024,16 @@
         <v>14</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>38</v>
       </c>
       <c r="BB10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC10" t="n">
         <v>24</v>
@@ -3048,25 +3048,25 @@
         <v>20</v>
       </c>
       <c r="BG10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BH10" t="n">
         <v>3.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN10" t="n">
         <v>5.5</v>
@@ -3075,16 +3075,16 @@
         <v>4.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
@@ -3096,13 +3096,13 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G11" t="n">
         <v>1.57</v>
@@ -3152,7 +3152,7 @@
         <v>6.6</v>
       </c>
       <c r="I11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
@@ -3161,7 +3161,7 @@
         <v>4.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -3170,28 +3170,28 @@
         <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W11" t="n">
         <v>2.74</v>
@@ -3200,7 +3200,7 @@
         <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z11" t="n">
         <v>60</v>
@@ -3209,22 +3209,22 @@
         <v>700</v>
       </c>
       <c r="AB11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF11" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AG11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
@@ -3245,7 +3245,7 @@
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO11" t="n">
         <v>100</v>
@@ -3257,13 +3257,13 @@
         <v>22</v>
       </c>
       <c r="AR11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AS11" t="n">
         <v>48</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>9.4</v>
@@ -3287,10 +3287,10 @@
         <v>48</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD11" t="n">
         <v>28</v>
@@ -3299,22 +3299,22 @@
         <v>80</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG11" t="n">
         <v>55</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3323,50 +3323,50 @@
         <v>100</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU11" t="n">
         <v>10</v>
       </c>
-      <c r="BQ11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BV11" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BW11" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H12" t="n">
         <v>4.4</v>
@@ -3409,7 +3409,7 @@
         <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
         <v>3.5</v>
@@ -3421,7 +3421,7 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.45</v>
@@ -3430,40 +3430,40 @@
         <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
         <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.9</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.91</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC12" t="n">
         <v>7.6</v>
@@ -3493,7 +3493,7 @@
         <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -3502,7 +3502,7 @@
         <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
         <v>9.4</v>
@@ -3514,16 +3514,16 @@
         <v>27</v>
       </c>
       <c r="AS12" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW12" t="n">
         <v>46</v>
@@ -3532,13 +3532,13 @@
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BB12" t="n">
         <v>22</v>
@@ -3553,13 +3553,13 @@
         <v>120</v>
       </c>
       <c r="BF12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG12" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI12" t="n">
         <v>2.52</v>
@@ -3568,7 +3568,7 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3586,28 +3586,28 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BR12" t="n">
         <v>36</v>
       </c>
       <c r="BS12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT12" t="n">
         <v>7.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
         <v>13</v>
@@ -3616,11 +3616,11 @@
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.02</v>
-      </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
         <v>3.45</v>
@@ -3681,7 +3681,7 @@
         <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q13" t="n">
         <v>2.4</v>
@@ -3693,34 +3693,34 @@
         <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V13" t="n">
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
         <v>10.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
         <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB13" t="n">
         <v>7.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
         <v>19.5</v>
@@ -3753,16 +3753,16 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>110</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
         <v>29</v>
@@ -3780,7 +3780,7 @@
         <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3789,40 +3789,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
         <v>75</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
         <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE13" t="n">
         <v>120</v>
       </c>
       <c r="BF13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG13" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BJ13" t="n">
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3840,41 +3840,41 @@
         <v>16</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW13" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -3911,16 +3911,16 @@
         <v>2.54</v>
       </c>
       <c r="H14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
         <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
         <v>1.5</v>
@@ -3929,31 +3929,31 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
         <v>1.65</v>
@@ -4001,7 +4001,7 @@
         <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
@@ -4025,7 +4025,7 @@
         <v>48</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
@@ -4088,7 +4088,7 @@
         <v>5.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP14" t="n">
         <v>20</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>4.7</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I15" t="n">
         <v>2.12</v>
@@ -4174,7 +4174,7 @@
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.58</v>
@@ -4201,7 +4201,7 @@
         <v>5.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U15" t="n">
         <v>1.72</v>
@@ -4210,7 +4210,7 @@
         <v>1.89</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
         <v>9</v>
@@ -4243,7 +4243,7 @@
         <v>23</v>
       </c>
       <c r="AH15" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
         <v>75</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="H16" t="n">
         <v>5.3</v>
@@ -4425,7 +4425,7 @@
         <v>5.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
         <v>3.45</v>
@@ -4455,19 +4455,19 @@
         <v>5.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
         <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y16" t="n">
         <v>15</v>
@@ -4476,7 +4476,7 @@
         <v>48</v>
       </c>
       <c r="AA16" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB16" t="n">
         <v>6.2</v>
@@ -4488,28 +4488,28 @@
         <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AF16" t="n">
         <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
         <v>36</v>
       </c>
       <c r="AI16" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ16" t="n">
         <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
         <v>310</v>
@@ -4518,7 +4518,7 @@
         <v>27</v>
       </c>
       <c r="AO16" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AP16" t="n">
         <v>7.2</v>
@@ -4527,13 +4527,13 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
@@ -4542,7 +4542,7 @@
         <v>20</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
         <v>8.6</v>
@@ -4563,80 +4563,80 @@
         <v>23</v>
       </c>
       <c r="BD16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF16" t="n">
         <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BJ16" t="n">
         <v>13</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BN16" t="n">
         <v>4.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP16" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
         <v>44</v>
       </c>
       <c r="BS16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I17" t="n">
         <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
         <v>3.85</v>
@@ -4691,16 +4691,16 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
         <v>1.3</v>
@@ -4709,7 +4709,7 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U17" t="n">
         <v>1.92</v>
@@ -4718,7 +4718,7 @@
         <v>1.24</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
@@ -4730,7 +4730,7 @@
         <v>44</v>
       </c>
       <c r="AA17" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB17" t="n">
         <v>8.6</v>
@@ -4772,19 +4772,19 @@
         <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4820,7 +4820,7 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF17" t="n">
         <v>13</v>
@@ -4829,13 +4829,13 @@
         <v>55</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK17" t="n">
         <v>8.6</v>
@@ -4844,25 +4844,25 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BN17" t="n">
         <v>4.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP17" t="n">
         <v>14</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR17" t="n">
         <v>32</v>
       </c>
       <c r="BS17" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT17" t="n">
         <v>8.4</v>
@@ -4874,23 +4874,23 @@
         <v>60</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX17" t="n">
         <v>75</v>
       </c>
       <c r="BY17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ17" t="n">
         <v>28</v>
       </c>
       <c r="CA17" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,60 +843,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="G2" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.38</v>
+        <v>5.8</v>
       </c>
       <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.4</v>
       </c>
-      <c r="J2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.84</v>
-      </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="S2" t="n">
-        <v>2.36</v>
+        <v>21</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -926,22 +926,22 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.15</v>
+        <v>1.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -950,7 +950,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.66</v>
+        <v>1.48</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.15</v>
+        <v>170</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.1</v>
+        <v>70</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.15</v>
+        <v>140</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.15</v>
+        <v>9.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.98</v>
+        <v>44</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.98</v>
+        <v>44</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,234 +1097,234 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>2.56</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>2.96</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S3" t="n">
         <v>3.05</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
         <v>4.1</v>
       </c>
-      <c r="T3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>3.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>40</v>
+        <v>990</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>870</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF3" t="n">
         <v>42</v>
       </c>
-      <c r="AK3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>440</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>25</v>
-      </c>
       <c r="BG3" t="n">
-        <v>30</v>
+        <v>2.84</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,244 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>120</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>260</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>200</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BN4" t="n">
         <v>1.21</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X4" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO4" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.86</v>
+        <v>5.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.22</v>
+        <v>5.6</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.31</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>27</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>880</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>370</v>
+      </c>
+      <c r="AF5" t="n">
         <v>4.6</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AG5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>380</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>32</v>
       </c>
-      <c r="AA5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="BA5" t="n">
+        <v>250</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF5" t="n">
         <v>19</v>
       </c>
-      <c r="AE5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>18</v>
-      </c>
       <c r="BG5" t="n">
-        <v>44</v>
+        <v>330</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>140</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.6</v>
+        <v>1.12</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>15.5</v>
+        <v>880</v>
       </c>
       <c r="BQ5" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="G6" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W6" t="n">
         <v>3.05</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.26</v>
-      </c>
       <c r="X6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>880</v>
       </c>
       <c r="AE6" t="n">
         <v>110</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="n">
-        <v>190</v>
+        <v>490</v>
       </c>
       <c r="AN6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>380</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>16</v>
       </c>
-      <c r="AO6" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA6" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>28</v>
-      </c>
       <c r="BB6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="BD6" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BE6" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="BF6" t="n">
-        <v>14.5</v>
+        <v>38</v>
       </c>
       <c r="BG6" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.78</v>
+        <v>6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="BK6" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>140</v>
+        <v>6</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.2</v>
+        <v>1.09</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>13</v>
+        <v>800</v>
       </c>
       <c r="BQ6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="BX6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,235 +2113,235 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Ivinhema FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Asa AL</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="G7" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>2.14</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI7" t="n">
         <v>2.44</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL7" t="n">
+      <c r="BJ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>180</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP7" t="n">
         <v>55</v>
       </c>
-      <c r="AM7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="BQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY7" t="n">
         <v>10</v>
       </c>
-      <c r="AR7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>130</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie D</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,45 +2367,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ivinhema FC</t>
+          <t>Amazonas FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asa AL</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7</v>
+        <v>1.88</v>
       </c>
       <c r="G8" t="n">
-        <v>5.3</v>
+        <v>1.96</v>
       </c>
       <c r="H8" t="n">
-        <v>1.99</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.12</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
         <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
         <v>1.57</v>
@@ -2417,201 +2417,201 @@
         <v>2.78</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>1.89</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX8" t="n">
         <v>8.6</v>
       </c>
-      <c r="Y8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA8" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB8" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ8" t="n">
         <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>60</v>
+        <v>16.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,493 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G9" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X9" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA9" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>420</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
         <v>13</v>
       </c>
-      <c r="AT9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BN9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV9" t="n">
         <v>60</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
       </c>
       <c r="BW9" t="n">
         <v>10.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Tecnico Universitario</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>28</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
